--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/28,07,26 ПОКОМ КИ/дв 28,07,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/28,07,26 ПОКОМ КИ/дв 28,07,26 днрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\28,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD220CCB-6A1D-40B6-8323-3D2D3CA31A80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DFB400-EA04-4046-8C3C-9EBAEC8805AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="193">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -1098,14 +1098,18 @@
     <col min="8" max="8" width="5" customWidth="1"/>
     <col min="9" max="9" width="8.5703125" customWidth="1"/>
     <col min="10" max="10" width="1" customWidth="1"/>
-    <col min="11" max="24" width="7" customWidth="1"/>
+    <col min="11" max="13" width="7" customWidth="1"/>
+    <col min="14" max="14" width="5.85546875" customWidth="1"/>
+    <col min="15" max="17" width="7" customWidth="1"/>
+    <col min="18" max="21" width="6.28515625" customWidth="1"/>
+    <col min="22" max="24" width="7" customWidth="1"/>
     <col min="25" max="27" width="7" style="20" customWidth="1"/>
     <col min="28" max="28" width="7" customWidth="1"/>
     <col min="29" max="30" width="5" customWidth="1"/>
     <col min="31" max="38" width="6.7109375" customWidth="1"/>
     <col min="39" max="39" width="6.42578125" customWidth="1"/>
-    <col min="40" max="42" width="7" customWidth="1"/>
-    <col min="43" max="50" width="3" customWidth="1"/>
+    <col min="40" max="43" width="7" customWidth="1"/>
+    <col min="44" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
@@ -1347,7 +1351,9 @@
       <c r="AP3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AQ3" s="1"/>
+      <c r="AQ3" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="AR3" s="1"/>
       <c r="AS3" s="1"/>
       <c r="AT3" s="1"/>
@@ -1447,7 +1453,9 @@
       <c r="AP4" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="AQ4" s="1"/>
+      <c r="AQ4" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="AR4" s="1"/>
       <c r="AS4" s="1"/>
       <c r="AT4" s="1"/>
@@ -1592,7 +1600,10 @@
         <f t="shared" si="4"/>
         <v>17567</v>
       </c>
-      <c r="AQ5" s="1"/>
+      <c r="AQ5" s="4">
+        <f t="shared" ref="AQ5" si="5">SUM(AQ6:AQ495)</f>
+        <v>12408</v>
+      </c>
       <c r="AR5" s="1"/>
       <c r="AS5" s="1"/>
       <c r="AT5" s="1"/>
@@ -1634,11 +1645,11 @@
         <v>2308.4839999999999</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L37" si="5">E6-K6</f>
+        <f t="shared" ref="L6:L37" si="6">E6-K6</f>
         <v>-129.14300000000003</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M37" si="6">E6-N6+P6</f>
+        <f t="shared" ref="M6:M37" si="7">E6-N6+P6</f>
         <v>2072.6769999999997</v>
       </c>
       <c r="N6" s="1">
@@ -1718,7 +1729,10 @@
         <f>ROUND(G6*AA6,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ6" s="1"/>
+      <c r="AQ6" s="1">
+        <f>ROUND(G6*AB6,0)</f>
+        <v>0</v>
+      </c>
       <c r="AR6" s="1"/>
       <c r="AS6" s="1"/>
       <c r="AT6" s="1"/>
@@ -1760,11 +1774,11 @@
         <v>1498.2260000000001</v>
       </c>
       <c r="L7" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-25.324000000000069</v>
       </c>
       <c r="M7" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>971.37900000000002</v>
       </c>
       <c r="N7" s="1"/>
@@ -1783,7 +1797,7 @@
         <v>269.7097379999999</v>
       </c>
       <c r="W7" s="1">
-        <f t="shared" ref="W7:W70" si="7">M7/5</f>
+        <f t="shared" ref="W7:W70" si="8">M7/5</f>
         <v>194.2758</v>
       </c>
       <c r="X7" s="5">
@@ -1791,7 +1805,7 @@
         <v>284.72726200000034</v>
       </c>
       <c r="Y7" s="5">
-        <f t="shared" ref="Y7:Y70" si="8">X7-Z7-AA7</f>
+        <f t="shared" ref="Y7:Y70" si="9">X7-Z7-AA7</f>
         <v>284.72726200000034</v>
       </c>
       <c r="Z7" s="5"/>
@@ -1800,11 +1814,11 @@
         <v>800</v>
       </c>
       <c r="AC7" s="1">
-        <f t="shared" ref="AC7:AC70" si="9">(F7+O7+Q7+R7+S7+T7+U7+V7+X7+AB7)/W7</f>
+        <f t="shared" ref="AC7:AC70" si="10">(F7+O7+Q7+R7+S7+T7+U7+V7+X7+AB7)/W7</f>
         <v>10.000000000000002</v>
       </c>
       <c r="AD7" s="1">
-        <f t="shared" ref="AD7:AD70" si="10">(F7+O7+Q7+R7+S7+T7+U7+V7)/W7</f>
+        <f t="shared" ref="AD7:AD70" si="11">(F7+O7+Q7+R7+S7+T7+U7+V7)/W7</f>
         <v>4.4165600553440001</v>
       </c>
       <c r="AE7" s="1">
@@ -1833,18 +1847,21 @@
       </c>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1">
-        <f t="shared" ref="AN7:AN70" si="11">ROUND(G7*Y7,0)</f>
+        <f t="shared" ref="AN7:AN70" si="12">ROUND(G7*Y7,0)</f>
         <v>285</v>
       </c>
       <c r="AO7" s="1">
-        <f t="shared" ref="AO7:AO70" si="12">ROUND(G7*Z7,0)</f>
+        <f t="shared" ref="AO7:AO70" si="13">ROUND(G7*Z7,0)</f>
         <v>0</v>
       </c>
       <c r="AP7" s="1">
-        <f t="shared" ref="AP7:AP70" si="13">ROUND(G7*AA7,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="1"/>
+        <f t="shared" ref="AP7:AQ70" si="14">ROUND(G7*AA7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="1">
+        <f t="shared" ref="AQ7:AQ70" si="15">ROUND(G7*AB7,0)</f>
+        <v>800</v>
+      </c>
       <c r="AR7" s="1"/>
       <c r="AS7" s="1"/>
       <c r="AT7" s="1"/>
@@ -1886,11 +1903,11 @@
         <v>3781.28</v>
       </c>
       <c r="L8" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-249.39700000000039</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3008.011</v>
       </c>
       <c r="N8" s="1"/>
@@ -1909,11 +1926,11 @@
         <v>0</v>
       </c>
       <c r="W8" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>601.60220000000004</v>
       </c>
       <c r="X8" s="5">
-        <f t="shared" ref="X8:X14" si="14">11*W8-V8-U8-T8-S8-R8-Q8-O8-F8-AB8</f>
+        <f t="shared" ref="X8:X14" si="16">11*W8-V8-U8-T8-S8-R8-Q8-O8-F8-AB8</f>
         <v>1387.815699220002</v>
       </c>
       <c r="Y8" s="5">
@@ -1931,7 +1948,7 @@
         <v>11</v>
       </c>
       <c r="AD8" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.8700096189475337</v>
       </c>
       <c r="AE8" s="1">
@@ -1960,18 +1977,21 @@
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="AO8" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP8" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>500</v>
       </c>
-      <c r="AQ8" s="1"/>
+      <c r="AQ8" s="1">
+        <f t="shared" si="15"/>
+        <v>2300</v>
+      </c>
       <c r="AR8" s="1"/>
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
@@ -2011,11 +2031,11 @@
         <v>17</v>
       </c>
       <c r="L9" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-6</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="N9" s="1"/>
@@ -2032,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="X9" s="5">
@@ -2040,18 +2060,18 @@
         <v>13</v>
       </c>
       <c r="Y9" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
       <c r="AB9" s="5"/>
       <c r="AC9" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="AD9" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.0909090909090908</v>
       </c>
       <c r="AE9" s="1">
@@ -2082,18 +2102,21 @@
         <v>46</v>
       </c>
       <c r="AN9" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="AO9" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP9" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR9" s="1"/>
       <c r="AS9" s="1"/>
       <c r="AT9" s="1"/>
@@ -2135,11 +2158,11 @@
         <v>4712</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1588.645</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3123.355</v>
       </c>
       <c r="N10" s="1"/>
@@ -2156,14 +2179,14 @@
         <v>104.554</v>
       </c>
       <c r="W10" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>624.67100000000005</v>
       </c>
       <c r="X10" s="5">
         <v>2000</v>
       </c>
       <c r="Y10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="Z10" s="5"/>
@@ -2172,11 +2195,11 @@
       </c>
       <c r="AB10" s="5"/>
       <c r="AC10" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.8654843909834131</v>
       </c>
       <c r="AD10" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.6637990238061313</v>
       </c>
       <c r="AE10" s="1">
@@ -2207,18 +2230,21 @@
         <v>49</v>
       </c>
       <c r="AN10" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>450</v>
       </c>
       <c r="AO10" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP10" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>450</v>
       </c>
-      <c r="AQ10" s="1"/>
+      <c r="AQ10" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR10" s="1"/>
       <c r="AS10" s="1"/>
       <c r="AT10" s="1"/>
@@ -2260,11 +2286,11 @@
         <v>5939</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-955.17100000000028</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3858.8289999999997</v>
       </c>
       <c r="N11" s="1"/>
@@ -2283,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="W11" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>771.7657999999999</v>
       </c>
       <c r="X11" s="5">
@@ -2291,7 +2317,7 @@
         <v>4989.4869999999992</v>
       </c>
       <c r="Y11" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1989.4869999999992</v>
       </c>
       <c r="Z11" s="5"/>
@@ -2300,11 +2326,11 @@
       </c>
       <c r="AB11" s="5"/>
       <c r="AC11" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="AD11" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.5349726562125454</v>
       </c>
       <c r="AE11" s="1">
@@ -2333,18 +2359,21 @@
       </c>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>895</v>
       </c>
       <c r="AO11" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP11" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1350</v>
       </c>
-      <c r="AQ11" s="1"/>
+      <c r="AQ11" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR11" s="1"/>
       <c r="AS11" s="1"/>
       <c r="AT11" s="1"/>
@@ -2386,11 +2415,11 @@
         <v>160</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-37</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>123</v>
       </c>
       <c r="N12" s="1"/>
@@ -2407,26 +2436,26 @@
         <v>0</v>
       </c>
       <c r="W12" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>24.6</v>
       </c>
       <c r="X12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>150.60000000000002</v>
       </c>
       <c r="Y12" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>150.60000000000002</v>
       </c>
       <c r="Z12" s="5"/>
       <c r="AA12" s="5"/>
       <c r="AB12" s="5"/>
       <c r="AC12" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD12" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.8780487804878048</v>
       </c>
       <c r="AE12" s="1">
@@ -2455,18 +2484,21 @@
       </c>
       <c r="AM12" s="1"/>
       <c r="AN12" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26</v>
       </c>
       <c r="AO12" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP12" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR12" s="1"/>
       <c r="AS12" s="1"/>
       <c r="AT12" s="1"/>
@@ -2508,11 +2540,11 @@
         <v>32</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-16</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="N13" s="1"/>
@@ -2529,25 +2561,25 @@
         <v>0</v>
       </c>
       <c r="W13" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.2</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z13" s="5"/>
       <c r="AA13" s="5"/>
       <c r="AB13" s="5"/>
       <c r="AC13" s="1">
-        <f t="shared" si="9"/>
-        <v>31.875</v>
-      </c>
-      <c r="AD13" s="1">
         <f t="shared" si="10"/>
         <v>31.875</v>
       </c>
+      <c r="AD13" s="1">
+        <f t="shared" si="11"/>
+        <v>31.875</v>
+      </c>
       <c r="AE13" s="1">
         <v>1</v>
       </c>
@@ -2574,18 +2606,21 @@
       </c>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO13" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR13" s="1"/>
       <c r="AS13" s="1"/>
       <c r="AT13" s="1"/>
@@ -2627,11 +2662,11 @@
         <v>440</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-32</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>326</v>
       </c>
       <c r="N14" s="1"/>
@@ -2650,26 +2685,26 @@
         <v>0</v>
       </c>
       <c r="W14" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>65.2</v>
       </c>
       <c r="X14" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>384.20000000000005</v>
       </c>
       <c r="Y14" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>384.20000000000005</v>
       </c>
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
       <c r="AC14" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD14" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.1073619631901837</v>
       </c>
       <c r="AE14" s="1">
@@ -2698,18 +2733,21 @@
       </c>
       <c r="AM14" s="1"/>
       <c r="AN14" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>65</v>
       </c>
       <c r="AO14" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP14" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR14" s="1"/>
       <c r="AS14" s="1"/>
       <c r="AT14" s="1"/>
@@ -2743,11 +2781,11 @@
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N15" s="13"/>
@@ -2760,25 +2798,25 @@
       <c r="U15" s="13"/>
       <c r="V15" s="13"/>
       <c r="W15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X15" s="15"/>
       <c r="Y15" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z15" s="15"/>
       <c r="AA15" s="15"/>
       <c r="AB15" s="15"/>
       <c r="AC15" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD15" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD15" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE15" s="13">
         <v>0</v>
       </c>
@@ -2807,18 +2845,21 @@
         <v>183</v>
       </c>
       <c r="AN15" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO15" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP15" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1"/>
       <c r="AT15" s="1"/>
@@ -2860,11 +2901,11 @@
         <v>4181.1580000000004</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-207.30100000000039</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3973.857</v>
       </c>
       <c r="N16" s="1"/>
@@ -2881,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="W16" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>794.77139999999997</v>
       </c>
       <c r="X16" s="5">
@@ -2899,11 +2940,11 @@
       </c>
       <c r="AB16" s="5"/>
       <c r="AC16" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="AD16" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.4795836890960095</v>
       </c>
       <c r="AE16" s="1">
@@ -2932,18 +2973,21 @@
       </c>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1737</v>
       </c>
       <c r="AO16" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>800</v>
       </c>
       <c r="AP16" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
-      <c r="AQ16" s="1"/>
+      <c r="AQ16" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1"/>
       <c r="AT16" s="1"/>
@@ -2985,11 +3029,11 @@
         <v>3419.5320000000002</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-300.87000000000035</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3118.6619999999998</v>
       </c>
       <c r="N17" s="1"/>
@@ -3006,12 +3050,12 @@
         <v>0</v>
       </c>
       <c r="W17" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>623.73239999999998</v>
       </c>
       <c r="X17" s="5"/>
       <c r="Y17" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z17" s="5"/>
@@ -3020,11 +3064,11 @@
         <v>1400</v>
       </c>
       <c r="AC17" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11.141558170779648</v>
       </c>
       <c r="AD17" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.8970058595641337</v>
       </c>
       <c r="AE17" s="1">
@@ -3053,18 +3097,21 @@
       </c>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO17" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP17" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="1">
+        <f t="shared" si="15"/>
+        <v>1400</v>
+      </c>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1"/>
       <c r="AT17" s="1"/>
@@ -3106,11 +3153,11 @@
         <v>486.54700000000003</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-176.26100000000002</v>
       </c>
       <c r="M18" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>182.53899999999999</v>
       </c>
       <c r="N18" s="1"/>
@@ -3129,25 +3176,25 @@
         <v>126.8083199999999</v>
       </c>
       <c r="W18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>36.507799999999996</v>
       </c>
       <c r="X18" s="5"/>
       <c r="Y18" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
       <c r="AB18" s="5"/>
       <c r="AC18" s="1">
-        <f t="shared" si="9"/>
-        <v>11.249276045119124</v>
-      </c>
-      <c r="AD18" s="1">
         <f t="shared" si="10"/>
         <v>11.249276045119124</v>
       </c>
+      <c r="AD18" s="1">
+        <f t="shared" si="11"/>
+        <v>11.249276045119124</v>
+      </c>
       <c r="AE18" s="1">
         <v>45.231999999999992</v>
       </c>
@@ -3174,18 +3221,21 @@
       </c>
       <c r="AM18" s="1"/>
       <c r="AN18" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO18" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP18" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR18" s="1"/>
       <c r="AS18" s="1"/>
       <c r="AT18" s="1"/>
@@ -3223,11 +3273,11 @@
         <v>5</v>
       </c>
       <c r="L19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-2.5259999999999998</v>
       </c>
       <c r="M19" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.4740000000000002</v>
       </c>
       <c r="N19" s="13"/>
@@ -3240,25 +3290,25 @@
       <c r="U19" s="13"/>
       <c r="V19" s="13"/>
       <c r="W19" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.49480000000000002</v>
       </c>
       <c r="X19" s="15"/>
       <c r="Y19" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z19" s="15"/>
       <c r="AA19" s="15"/>
       <c r="AB19" s="15"/>
       <c r="AC19" s="13">
-        <f t="shared" si="9"/>
-        <v>-10.052546483427648</v>
-      </c>
-      <c r="AD19" s="13">
         <f t="shared" si="10"/>
         <v>-10.052546483427648</v>
       </c>
+      <c r="AD19" s="13">
+        <f t="shared" si="11"/>
+        <v>-10.052546483427648</v>
+      </c>
       <c r="AE19" s="13">
         <v>0</v>
       </c>
@@ -3285,18 +3335,21 @@
       </c>
       <c r="AM19" s="13"/>
       <c r="AN19" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO19" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP19" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1"/>
       <c r="AT19" s="1"/>
@@ -3326,11 +3379,11 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M20" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N20" s="13"/>
@@ -3347,25 +3400,25 @@
         <v>0</v>
       </c>
       <c r="W20" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X20" s="15"/>
       <c r="Y20" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z20" s="15"/>
       <c r="AA20" s="15"/>
       <c r="AB20" s="15"/>
       <c r="AC20" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD20" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD20" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE20" s="13">
         <v>0</v>
       </c>
@@ -3394,18 +3447,21 @@
         <v>61</v>
       </c>
       <c r="AN20" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO20" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP20" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR20" s="1"/>
       <c r="AS20" s="1"/>
       <c r="AT20" s="1"/>
@@ -3447,11 +3503,11 @@
         <v>5.4</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.53200000000000003</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.9320000000000004</v>
       </c>
       <c r="N21" s="1"/>
@@ -3468,25 +3524,25 @@
         <v>0</v>
       </c>
       <c r="W21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.1864000000000001</v>
       </c>
       <c r="X21" s="5"/>
       <c r="Y21" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z21" s="5"/>
       <c r="AA21" s="5"/>
       <c r="AB21" s="5"/>
       <c r="AC21" s="1">
-        <f t="shared" si="9"/>
-        <v>15.160148347943357</v>
-      </c>
-      <c r="AD21" s="1">
         <f t="shared" si="10"/>
         <v>15.160148347943357</v>
       </c>
+      <c r="AD21" s="1">
+        <f t="shared" si="11"/>
+        <v>15.160148347943357</v>
+      </c>
       <c r="AE21" s="1">
         <v>0.42980000000000002</v>
       </c>
@@ -3513,18 +3569,21 @@
       </c>
       <c r="AM21" s="1"/>
       <c r="AN21" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO21" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP21" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR21" s="1"/>
       <c r="AS21" s="1"/>
       <c r="AT21" s="1"/>
@@ -3566,11 +3625,11 @@
         <v>7016.96</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-184.83200000000033</v>
       </c>
       <c r="M22" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4352.4179999999997</v>
       </c>
       <c r="N22" s="1">
@@ -3591,15 +3650,15 @@
         <v>0</v>
       </c>
       <c r="W22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>870.48359999999991</v>
       </c>
       <c r="X22" s="5">
-        <f t="shared" ref="X22" si="15">11*W22-V22-U22-T22-S22-R22-Q22-O22-F22-AB22</f>
+        <f t="shared" ref="X22" si="17">11*W22-V22-U22-T22-S22-R22-Q22-O22-F22-AB22</f>
         <v>5401.5915999999988</v>
       </c>
       <c r="Y22" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1901.5915999999988</v>
       </c>
       <c r="Z22" s="5"/>
@@ -3608,11 +3667,11 @@
       </c>
       <c r="AB22" s="5"/>
       <c r="AC22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD22" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.7947233009329535</v>
       </c>
       <c r="AE22" s="1">
@@ -3641,18 +3700,21 @@
       </c>
       <c r="AM22" s="1"/>
       <c r="AN22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1902</v>
       </c>
       <c r="AO22" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP22" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3500</v>
       </c>
-      <c r="AQ22" s="1"/>
+      <c r="AQ22" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1"/>
       <c r="AT22" s="1"/>
@@ -3690,11 +3752,11 @@
         <v>7.5</v>
       </c>
       <c r="L23" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-6.9999999999996732E-3</v>
       </c>
       <c r="M23" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.4930000000000003</v>
       </c>
       <c r="N23" s="13"/>
@@ -3707,25 +3769,25 @@
       <c r="U23" s="13"/>
       <c r="V23" s="13"/>
       <c r="W23" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4986000000000002</v>
       </c>
       <c r="X23" s="15"/>
       <c r="Y23" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z23" s="15"/>
       <c r="AA23" s="15"/>
       <c r="AB23" s="15"/>
       <c r="AC23" s="13">
-        <f t="shared" si="9"/>
-        <v>-5</v>
-      </c>
-      <c r="AD23" s="13">
         <f t="shared" si="10"/>
         <v>-5</v>
       </c>
+      <c r="AD23" s="13">
+        <f t="shared" si="11"/>
+        <v>-5</v>
+      </c>
       <c r="AE23" s="13">
         <v>0</v>
       </c>
@@ -3752,18 +3814,21 @@
       </c>
       <c r="AM23" s="13"/>
       <c r="AN23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO23" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP23" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR23" s="1"/>
       <c r="AS23" s="1"/>
       <c r="AT23" s="1"/>
@@ -3805,11 +3870,11 @@
         <v>602.99</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.9950000000000045</v>
       </c>
       <c r="M24" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>561.34500000000003</v>
       </c>
       <c r="N24" s="1">
@@ -3828,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>112.26900000000001</v>
       </c>
       <c r="X24" s="5">
@@ -3836,7 +3901,7 @@
         <v>643.26725999999985</v>
       </c>
       <c r="Y24" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>343.26725999999985</v>
       </c>
       <c r="Z24" s="5"/>
@@ -3845,11 +3910,11 @@
       </c>
       <c r="AB24" s="5"/>
       <c r="AC24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="AD24" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.270303823851644</v>
       </c>
       <c r="AE24" s="1">
@@ -3878,18 +3943,21 @@
       </c>
       <c r="AM24" s="1"/>
       <c r="AN24" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>343</v>
       </c>
       <c r="AO24" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>300</v>
       </c>
-      <c r="AQ24" s="1"/>
+      <c r="AQ24" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR24" s="1"/>
       <c r="AS24" s="1"/>
       <c r="AT24" s="1"/>
@@ -3931,11 +3999,11 @@
         <v>1342.4390000000001</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-62.550000000000182</v>
       </c>
       <c r="M25" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1279.8889999999999</v>
       </c>
       <c r="N25" s="1"/>
@@ -3952,15 +4020,15 @@
         <v>0</v>
       </c>
       <c r="W25" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>255.97779999999997</v>
       </c>
       <c r="X25" s="5">
-        <f t="shared" ref="X25" si="16">11*W25-V25-U25-T25-S25-R25-Q25-O25-F25-AB25</f>
+        <f t="shared" ref="X25" si="18">11*W25-V25-U25-T25-S25-R25-Q25-O25-F25-AB25</f>
         <v>1523.0627999999999</v>
       </c>
       <c r="Y25" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>723.06279999999992</v>
       </c>
       <c r="Z25" s="5"/>
@@ -3969,11 +4037,11 @@
       </c>
       <c r="AB25" s="5"/>
       <c r="AC25" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD25" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.050019962668638</v>
       </c>
       <c r="AE25" s="1">
@@ -4002,18 +4070,21 @@
       </c>
       <c r="AM25" s="1"/>
       <c r="AN25" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>723</v>
       </c>
       <c r="AO25" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP25" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>800</v>
       </c>
-      <c r="AQ25" s="1"/>
+      <c r="AQ25" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR25" s="1"/>
       <c r="AS25" s="1"/>
       <c r="AT25" s="1"/>
@@ -4043,11 +4114,11 @@
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
       <c r="L26" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M26" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N26" s="13"/>
@@ -4064,25 +4135,25 @@
         <v>0</v>
       </c>
       <c r="W26" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X26" s="15"/>
       <c r="Y26" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z26" s="15"/>
       <c r="AA26" s="15"/>
       <c r="AB26" s="15"/>
       <c r="AC26" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD26" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD26" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE26" s="13">
         <v>0</v>
       </c>
@@ -4111,18 +4182,21 @@
         <v>61</v>
       </c>
       <c r="AN26" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO26" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP26" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR26" s="1"/>
       <c r="AS26" s="1"/>
       <c r="AT26" s="1"/>
@@ -4164,11 +4238,11 @@
         <v>2727.8589999999999</v>
       </c>
       <c r="L27" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-142.33599999999979</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2285.3140000000003</v>
       </c>
       <c r="N27" s="1"/>
@@ -4187,15 +4261,15 @@
         <v>0</v>
       </c>
       <c r="W27" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>457.06280000000004</v>
       </c>
       <c r="X27" s="5">
-        <f t="shared" ref="X27" si="17">11*W27-V27-U27-T27-S27-R27-Q27-O27-F27-AB27</f>
+        <f t="shared" ref="X27" si="19">11*W27-V27-U27-T27-S27-R27-Q27-O27-F27-AB27</f>
         <v>2784.0868000000005</v>
       </c>
       <c r="Y27" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>784.08680000000049</v>
       </c>
       <c r="Z27" s="5"/>
@@ -4204,11 +4278,11 @@
       </c>
       <c r="AB27" s="5"/>
       <c r="AC27" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD27" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.9087433936868186</v>
       </c>
       <c r="AE27" s="1">
@@ -4237,18 +4311,21 @@
       </c>
       <c r="AM27" s="1"/>
       <c r="AN27" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>784</v>
       </c>
       <c r="AO27" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP27" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
-      <c r="AQ27" s="1"/>
+      <c r="AQ27" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR27" s="1"/>
       <c r="AS27" s="1"/>
       <c r="AT27" s="1"/>
@@ -4290,11 +4367,11 @@
         <v>85.899000000000001</v>
       </c>
       <c r="L28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-2.7219999999999942</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>43.678000000000004</v>
       </c>
       <c r="N28" s="1"/>
@@ -4313,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="W28" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.7356000000000016</v>
       </c>
       <c r="X28" s="5">
@@ -4321,18 +4398,18 @@
         <v>49.604200000000006</v>
       </c>
       <c r="Y28" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>49.604200000000006</v>
       </c>
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
       <c r="AB28" s="5"/>
       <c r="AC28" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="AD28" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3216035532762487</v>
       </c>
       <c r="AE28" s="1">
@@ -4361,18 +4438,21 @@
       </c>
       <c r="AM28" s="1"/>
       <c r="AN28" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>50</v>
       </c>
       <c r="AO28" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP28" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR28" s="1"/>
       <c r="AS28" s="1"/>
       <c r="AT28" s="1"/>
@@ -4402,11 +4482,11 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M29" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N29" s="13"/>
@@ -4423,25 +4503,25 @@
         <v>0</v>
       </c>
       <c r="W29" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X29" s="15"/>
       <c r="Y29" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z29" s="15"/>
       <c r="AA29" s="15"/>
       <c r="AB29" s="15"/>
       <c r="AC29" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD29" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD29" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE29" s="13">
         <v>0</v>
       </c>
@@ -4470,18 +4550,21 @@
         <v>61</v>
       </c>
       <c r="AN29" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO29" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP29" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ29" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR29" s="1"/>
       <c r="AS29" s="1"/>
       <c r="AT29" s="1"/>
@@ -4511,11 +4594,11 @@
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
       <c r="L30" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M30" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N30" s="13"/>
@@ -4532,25 +4615,25 @@
         <v>0</v>
       </c>
       <c r="W30" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X30" s="15"/>
       <c r="Y30" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z30" s="15"/>
       <c r="AA30" s="15"/>
       <c r="AB30" s="15"/>
       <c r="AC30" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD30" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD30" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE30" s="13">
         <v>0</v>
       </c>
@@ -4579,18 +4662,21 @@
         <v>61</v>
       </c>
       <c r="AN30" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO30" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP30" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR30" s="1"/>
       <c r="AS30" s="1"/>
       <c r="AT30" s="1"/>
@@ -4632,11 +4718,11 @@
         <v>2963.3980000000001</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1119.1210000000001</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1844.277</v>
       </c>
       <c r="N31" s="1"/>
@@ -4655,7 +4741,7 @@
         <v>1201.7200419999999</v>
       </c>
       <c r="W31" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>368.85540000000003</v>
       </c>
       <c r="X31" s="5">
@@ -4663,7 +4749,7 @@
         <v>716.48535800000036</v>
       </c>
       <c r="Y31" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>316.48535800000036</v>
       </c>
       <c r="Z31" s="5"/>
@@ -4672,11 +4758,11 @@
       </c>
       <c r="AB31" s="5"/>
       <c r="AC31" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10.999999999999998</v>
       </c>
       <c r="AD31" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.057544072826369</v>
       </c>
       <c r="AE31" s="1">
@@ -4707,18 +4793,21 @@
         <v>73</v>
       </c>
       <c r="AN31" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>316</v>
       </c>
       <c r="AO31" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP31" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>400</v>
       </c>
-      <c r="AQ31" s="1"/>
+      <c r="AQ31" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR31" s="1"/>
       <c r="AS31" s="1"/>
       <c r="AT31" s="1"/>
@@ -4760,11 +4849,11 @@
         <v>117.364</v>
       </c>
       <c r="L32" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.1530000000000058</v>
       </c>
       <c r="M32" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>69.947000000000003</v>
       </c>
       <c r="N32" s="13"/>
@@ -4783,25 +4872,25 @@
         <v>0</v>
       </c>
       <c r="W32" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13.9894</v>
       </c>
       <c r="X32" s="15"/>
       <c r="Y32" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z32" s="15"/>
       <c r="AA32" s="15"/>
       <c r="AB32" s="15"/>
       <c r="AC32" s="13">
-        <f t="shared" si="9"/>
-        <v>-1.6441019629147784E-2</v>
-      </c>
-      <c r="AD32" s="13">
         <f t="shared" si="10"/>
         <v>-1.6441019629147784E-2</v>
       </c>
+      <c r="AD32" s="13">
+        <f t="shared" si="11"/>
+        <v>-1.6441019629147784E-2</v>
+      </c>
       <c r="AE32" s="13">
         <v>4.5703999999999994</v>
       </c>
@@ -4828,18 +4917,21 @@
       </c>
       <c r="AM32" s="13"/>
       <c r="AN32" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO32" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP32" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ32" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR32" s="1"/>
       <c r="AS32" s="1"/>
       <c r="AT32" s="1"/>
@@ -4881,11 +4973,11 @@
         <v>9268.5190000000002</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-2044.866</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5921.2660000000005</v>
       </c>
       <c r="N33" s="1">
@@ -4908,7 +5000,7 @@
         <v>2274.673775600003</v>
       </c>
       <c r="W33" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1184.2532000000001</v>
       </c>
       <c r="X33" s="5">
@@ -4925,11 +5017,11 @@
         <v>6000</v>
       </c>
       <c r="AC33" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.6961892929653901</v>
       </c>
       <c r="AD33" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-5.912283116482047E-2</v>
       </c>
       <c r="AE33" s="1">
@@ -4958,18 +5050,21 @@
       </c>
       <c r="AM33" s="1"/>
       <c r="AN33" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1200</v>
       </c>
       <c r="AO33" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP33" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>500</v>
       </c>
-      <c r="AQ33" s="1"/>
+      <c r="AQ33" s="1">
+        <f t="shared" si="15"/>
+        <v>6000</v>
+      </c>
       <c r="AR33" s="1"/>
       <c r="AS33" s="1"/>
       <c r="AT33" s="1"/>
@@ -4999,11 +5094,11 @@
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
       <c r="L34" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M34" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N34" s="13"/>
@@ -5020,25 +5115,25 @@
         <v>0</v>
       </c>
       <c r="W34" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X34" s="15"/>
       <c r="Y34" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z34" s="15"/>
       <c r="AA34" s="15"/>
       <c r="AB34" s="15"/>
       <c r="AC34" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD34" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD34" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE34" s="13">
         <v>0</v>
       </c>
@@ -5067,18 +5162,21 @@
         <v>61</v>
       </c>
       <c r="AN34" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO34" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP34" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR34" s="1"/>
       <c r="AS34" s="1"/>
       <c r="AT34" s="1"/>
@@ -5108,11 +5206,11 @@
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M35" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N35" s="13"/>
@@ -5129,25 +5227,25 @@
         <v>0</v>
       </c>
       <c r="W35" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X35" s="15"/>
       <c r="Y35" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z35" s="15"/>
       <c r="AA35" s="15"/>
       <c r="AB35" s="15"/>
       <c r="AC35" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD35" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD35" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE35" s="13">
         <v>0</v>
       </c>
@@ -5176,18 +5274,21 @@
         <v>61</v>
       </c>
       <c r="AN35" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO35" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP35" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR35" s="1"/>
       <c r="AS35" s="1"/>
       <c r="AT35" s="1"/>
@@ -5217,11 +5318,11 @@
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M36" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N36" s="13"/>
@@ -5238,25 +5339,25 @@
         <v>0</v>
       </c>
       <c r="W36" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X36" s="15"/>
       <c r="Y36" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z36" s="15"/>
       <c r="AA36" s="15"/>
       <c r="AB36" s="15"/>
       <c r="AC36" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD36" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD36" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE36" s="13">
         <v>0</v>
       </c>
@@ -5285,18 +5386,21 @@
         <v>61</v>
       </c>
       <c r="AN36" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO36" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP36" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR36" s="1"/>
       <c r="AS36" s="1"/>
       <c r="AT36" s="1"/>
@@ -5326,11 +5430,11 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M37" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N37" s="13"/>
@@ -5347,25 +5451,25 @@
         <v>0</v>
       </c>
       <c r="W37" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X37" s="15"/>
       <c r="Y37" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z37" s="15"/>
       <c r="AA37" s="15"/>
       <c r="AB37" s="15"/>
       <c r="AC37" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD37" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD37" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE37" s="13">
         <v>0</v>
       </c>
@@ -5394,18 +5498,21 @@
         <v>61</v>
       </c>
       <c r="AN37" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO37" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP37" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR37" s="1"/>
       <c r="AS37" s="1"/>
       <c r="AT37" s="1"/>
@@ -5447,11 +5554,11 @@
         <v>6117</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="18">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="20">E38-K38</f>
         <v>-806</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" ref="M38:M69" si="19">E38-N38+P38</f>
+        <f t="shared" ref="M38:M69" si="21">E38-N38+P38</f>
         <v>4387</v>
       </c>
       <c r="N38" s="1"/>
@@ -5470,11 +5577,11 @@
         <v>1391.9339999999991</v>
       </c>
       <c r="W38" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>877.4</v>
       </c>
       <c r="X38" s="5">
-        <f t="shared" ref="X38" si="20">11*W38-V38-U38-T38-S38-R38-Q38-O38-F38-AB38</f>
+        <f t="shared" ref="X38" si="22">11*W38-V38-U38-T38-S38-R38-Q38-O38-F38-AB38</f>
         <v>2536.4660000000003</v>
       </c>
       <c r="Y38" s="5">
@@ -5492,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="AD38" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.6899179393663086</v>
       </c>
       <c r="AE38" s="1">
@@ -5521,18 +5628,21 @@
       </c>
       <c r="AM38" s="1"/>
       <c r="AN38" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>480</v>
       </c>
       <c r="AO38" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP38" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>400</v>
       </c>
-      <c r="AQ38" s="1"/>
+      <c r="AQ38" s="1">
+        <f t="shared" si="15"/>
+        <v>1200</v>
+      </c>
       <c r="AR38" s="1"/>
       <c r="AS38" s="1"/>
       <c r="AT38" s="1"/>
@@ -5574,11 +5684,11 @@
         <v>1602</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-243</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>639</v>
       </c>
       <c r="N39" s="1"/>
@@ -5597,25 +5707,25 @@
         <v>0</v>
       </c>
       <c r="W39" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>127.8</v>
       </c>
       <c r="X39" s="5"/>
       <c r="Y39" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z39" s="5"/>
       <c r="AA39" s="5"/>
       <c r="AB39" s="5"/>
       <c r="AC39" s="1">
-        <f t="shared" si="9"/>
-        <v>11.664710485133021</v>
-      </c>
-      <c r="AD39" s="1">
         <f t="shared" si="10"/>
         <v>11.664710485133021</v>
       </c>
+      <c r="AD39" s="1">
+        <f t="shared" si="11"/>
+        <v>11.664710485133021</v>
+      </c>
       <c r="AE39" s="1">
         <v>67.2</v>
       </c>
@@ -5644,18 +5754,21 @@
         <v>126</v>
       </c>
       <c r="AN39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO39" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP39" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR39" s="1"/>
       <c r="AS39" s="1"/>
       <c r="AT39" s="1"/>
@@ -5697,11 +5810,11 @@
         <v>2110</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-320</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1508</v>
       </c>
       <c r="N40" s="1"/>
@@ -5720,15 +5833,15 @@
         <v>1095.0219999999999</v>
       </c>
       <c r="W40" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>301.60000000000002</v>
       </c>
       <c r="X40" s="5">
-        <f t="shared" ref="X40:X41" si="21">10*W40-V40-U40-T40-S40-R40-Q40-O40-F40-AB40</f>
+        <f t="shared" ref="X40:X41" si="23">10*W40-V40-U40-T40-S40-R40-Q40-O40-F40-AB40</f>
         <v>1763.9780000000001</v>
       </c>
       <c r="Y40" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>763.97800000000007</v>
       </c>
       <c r="Z40" s="5"/>
@@ -5737,11 +5850,11 @@
       </c>
       <c r="AB40" s="5"/>
       <c r="AC40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="AD40" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.1512665782493361</v>
       </c>
       <c r="AE40" s="1">
@@ -5770,18 +5883,21 @@
       </c>
       <c r="AM40" s="1"/>
       <c r="AN40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>306</v>
       </c>
       <c r="AO40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>400</v>
       </c>
-      <c r="AQ40" s="1"/>
+      <c r="AQ40" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR40" s="1"/>
       <c r="AS40" s="1"/>
       <c r="AT40" s="1"/>
@@ -5823,11 +5939,11 @@
         <v>809</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-175</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>634</v>
       </c>
       <c r="N41" s="1"/>
@@ -5844,15 +5960,15 @@
         <v>301.64999999999998</v>
       </c>
       <c r="W41" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>126.8</v>
       </c>
       <c r="X41" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>720.14</v>
       </c>
       <c r="Y41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>320.14</v>
       </c>
       <c r="Z41" s="5"/>
@@ -5861,11 +5977,11 @@
       </c>
       <c r="AB41" s="5"/>
       <c r="AC41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="AD41" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.3206624605678234</v>
       </c>
       <c r="AE41" s="1">
@@ -5894,18 +6010,21 @@
       </c>
       <c r="AM41" s="1"/>
       <c r="AN41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>128</v>
       </c>
       <c r="AO41" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>160</v>
       </c>
-      <c r="AQ41" s="1"/>
+      <c r="AQ41" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR41" s="1"/>
       <c r="AS41" s="1"/>
       <c r="AT41" s="1"/>
@@ -5935,11 +6054,11 @@
       <c r="J42" s="13"/>
       <c r="K42" s="13"/>
       <c r="L42" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M42" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N42" s="13"/>
@@ -5956,25 +6075,25 @@
         <v>0</v>
       </c>
       <c r="W42" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X42" s="15"/>
       <c r="Y42" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z42" s="15"/>
       <c r="AA42" s="15"/>
       <c r="AB42" s="15"/>
       <c r="AC42" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD42" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD42" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE42" s="13">
         <v>0</v>
       </c>
@@ -6003,18 +6122,21 @@
         <v>61</v>
       </c>
       <c r="AN42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO42" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP42" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR42" s="1"/>
       <c r="AS42" s="1"/>
       <c r="AT42" s="1"/>
@@ -6056,11 +6178,11 @@
         <v>292</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-16</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>276</v>
       </c>
       <c r="N43" s="1"/>
@@ -6077,15 +6199,15 @@
         <v>0</v>
       </c>
       <c r="W43" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>55.2</v>
       </c>
       <c r="X43" s="5">
-        <f t="shared" ref="X43:X51" si="22">11*W43-V43-U43-T43-S43-R43-Q43-O43-F43-AB43</f>
+        <f t="shared" ref="X43:X51" si="24">11*W43-V43-U43-T43-S43-R43-Q43-O43-F43-AB43</f>
         <v>336.20000000000005</v>
       </c>
       <c r="Y43" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>236.20000000000005</v>
       </c>
       <c r="Z43" s="5"/>
@@ -6094,11 +6216,11 @@
       </c>
       <c r="AB43" s="5"/>
       <c r="AC43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD43" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.9094202898550723</v>
       </c>
       <c r="AE43" s="1">
@@ -6127,18 +6249,21 @@
       </c>
       <c r="AM43" s="1"/>
       <c r="AN43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="AO43" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10</v>
       </c>
-      <c r="AQ43" s="1"/>
+      <c r="AQ43" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR43" s="1"/>
       <c r="AS43" s="1"/>
       <c r="AT43" s="1"/>
@@ -6180,11 +6305,11 @@
         <v>185</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-63</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>122</v>
       </c>
       <c r="N44" s="1"/>
@@ -6201,26 +6326,26 @@
         <v>0</v>
       </c>
       <c r="W44" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>24.4</v>
       </c>
       <c r="X44" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>99.399999999999977</v>
       </c>
       <c r="Y44" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>99.399999999999977</v>
       </c>
       <c r="Z44" s="5"/>
       <c r="AA44" s="5"/>
       <c r="AB44" s="5"/>
       <c r="AC44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.9262295081967213</v>
       </c>
       <c r="AE44" s="1">
@@ -6249,18 +6374,21 @@
       </c>
       <c r="AM44" s="1"/>
       <c r="AN44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>35</v>
       </c>
       <c r="AO44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP44" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ44" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR44" s="1"/>
       <c r="AS44" s="1"/>
       <c r="AT44" s="1"/>
@@ -6300,11 +6428,11 @@
         <v>17.8</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-4.3050000000000015</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>13.494999999999999</v>
       </c>
       <c r="N45" s="1"/>
@@ -6321,25 +6449,25 @@
         <v>16.10894</v>
       </c>
       <c r="W45" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.6989999999999998</v>
       </c>
       <c r="X45" s="5"/>
       <c r="Y45" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z45" s="5"/>
       <c r="AA45" s="5"/>
       <c r="AB45" s="5"/>
       <c r="AC45" s="1">
-        <f t="shared" si="9"/>
-        <v>15.226454242311966</v>
-      </c>
-      <c r="AD45" s="1">
         <f t="shared" si="10"/>
         <v>15.226454242311966</v>
       </c>
+      <c r="AD45" s="1">
+        <f t="shared" si="11"/>
+        <v>15.226454242311966</v>
+      </c>
       <c r="AE45" s="1">
         <v>4.2096</v>
       </c>
@@ -6366,18 +6494,21 @@
       </c>
       <c r="AM45" s="1"/>
       <c r="AN45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO45" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP45" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ45" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR45" s="1"/>
       <c r="AS45" s="1"/>
       <c r="AT45" s="1"/>
@@ -6419,11 +6550,11 @@
         <v>311</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-304</v>
       </c>
       <c r="M46" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="N46" s="1"/>
@@ -6440,25 +6571,25 @@
         <v>299.702</v>
       </c>
       <c r="W46" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4</v>
       </c>
       <c r="X46" s="5"/>
       <c r="Y46" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z46" s="5"/>
       <c r="AA46" s="5"/>
       <c r="AB46" s="5"/>
       <c r="AC46" s="1">
-        <f t="shared" si="9"/>
-        <v>196.21571428571428</v>
-      </c>
-      <c r="AD46" s="1">
         <f t="shared" si="10"/>
         <v>196.21571428571428</v>
       </c>
+      <c r="AD46" s="1">
+        <f t="shared" si="11"/>
+        <v>196.21571428571428</v>
+      </c>
       <c r="AE46" s="1">
         <v>0.2</v>
       </c>
@@ -6485,18 +6616,21 @@
       </c>
       <c r="AM46" s="1"/>
       <c r="AN46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO46" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP46" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR46" s="1"/>
       <c r="AS46" s="1"/>
       <c r="AT46" s="1"/>
@@ -6538,11 +6672,11 @@
         <v>335</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-85</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>250</v>
       </c>
       <c r="N47" s="1"/>
@@ -6561,12 +6695,12 @@
         <v>0</v>
       </c>
       <c r="W47" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="X47" s="5"/>
       <c r="Y47" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z47" s="5"/>
@@ -6575,11 +6709,11 @@
         <v>400</v>
       </c>
       <c r="AC47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10.2524</v>
       </c>
       <c r="AD47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.2524000000000002</v>
       </c>
       <c r="AE47" s="1">
@@ -6608,18 +6742,21 @@
       </c>
       <c r="AM47" s="1"/>
       <c r="AN47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP47" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ47" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="1">
+        <f t="shared" si="15"/>
+        <v>160</v>
+      </c>
       <c r="AR47" s="1"/>
       <c r="AS47" s="1"/>
       <c r="AT47" s="1"/>
@@ -6661,11 +6798,11 @@
         <v>63.2</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-18.389000000000003</v>
       </c>
       <c r="M48" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>44.811</v>
       </c>
       <c r="N48" s="1"/>
@@ -6682,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="W48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.9621999999999993</v>
       </c>
       <c r="X48" s="5">
@@ -6690,18 +6827,18 @@
         <v>53.349599999999995</v>
       </c>
       <c r="Y48" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>53.349599999999995</v>
       </c>
       <c r="Z48" s="5"/>
       <c r="AA48" s="5"/>
       <c r="AB48" s="5"/>
       <c r="AC48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="AD48" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0472651804244495</v>
       </c>
       <c r="AE48" s="1">
@@ -6730,18 +6867,21 @@
       </c>
       <c r="AM48" s="1"/>
       <c r="AN48" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>53</v>
       </c>
       <c r="AO48" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP48" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ48" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR48" s="1"/>
       <c r="AS48" s="1"/>
       <c r="AT48" s="1"/>
@@ -6783,11 +6923,11 @@
         <v>730</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-143</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>587</v>
       </c>
       <c r="N49" s="1"/>
@@ -6804,14 +6944,14 @@
         <v>70.88</v>
       </c>
       <c r="W49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>117.4</v>
       </c>
       <c r="X49" s="5">
         <v>200</v>
       </c>
       <c r="Y49" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>200</v>
       </c>
       <c r="Z49" s="5"/>
@@ -6820,11 +6960,11 @@
         <v>400</v>
       </c>
       <c r="AC49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.9649063032367984</v>
       </c>
       <c r="AD49" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.854173764906303</v>
       </c>
       <c r="AE49" s="1">
@@ -6855,18 +6995,21 @@
         <v>93</v>
       </c>
       <c r="AN49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>70</v>
       </c>
       <c r="AO49" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP49" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ49" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="1">
+        <f t="shared" si="15"/>
+        <v>140</v>
+      </c>
       <c r="AR49" s="1"/>
       <c r="AS49" s="1"/>
       <c r="AT49" s="1"/>
@@ -6908,11 +7051,11 @@
         <v>569</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-314</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>255</v>
       </c>
       <c r="N50" s="1"/>
@@ -6929,15 +7072,15 @@
         <v>0</v>
       </c>
       <c r="W50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>51</v>
       </c>
       <c r="X50" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>60</v>
       </c>
       <c r="Y50" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
       <c r="Z50" s="5"/>
@@ -6946,11 +7089,11 @@
         <v>200</v>
       </c>
       <c r="AC50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD50" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9019607843137258</v>
       </c>
       <c r="AE50" s="1">
@@ -6979,18 +7122,21 @@
       </c>
       <c r="AM50" s="1"/>
       <c r="AN50" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="AO50" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP50" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ50" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="1">
+        <f t="shared" si="15"/>
+        <v>80</v>
+      </c>
       <c r="AR50" s="1"/>
       <c r="AS50" s="1"/>
       <c r="AT50" s="1"/>
@@ -7032,11 +7178,11 @@
         <v>164.876</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-15.650000000000006</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>95.55</v>
       </c>
       <c r="N51" s="1"/>
@@ -7055,26 +7201,26 @@
         <v>81.053600000000003</v>
       </c>
       <c r="W51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>19.11</v>
       </c>
       <c r="X51" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>33.113399999999956</v>
       </c>
       <c r="Y51" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>33.113399999999956</v>
       </c>
       <c r="Z51" s="5"/>
       <c r="AA51" s="5"/>
       <c r="AB51" s="5"/>
       <c r="AC51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD51" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.2672213500784952</v>
       </c>
       <c r="AE51" s="1">
@@ -7103,18 +7249,21 @@
       </c>
       <c r="AM51" s="1"/>
       <c r="AN51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
       <c r="AO51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP51" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ51" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR51" s="1"/>
       <c r="AS51" s="1"/>
       <c r="AT51" s="1"/>
@@ -7156,11 +7305,11 @@
         <v>430.79</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-33.813000000000045</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>396.97699999999998</v>
       </c>
       <c r="N52" s="1"/>
@@ -7177,25 +7326,25 @@
         <v>0</v>
       </c>
       <c r="W52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>79.395399999999995</v>
       </c>
       <c r="X52" s="5"/>
       <c r="Y52" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z52" s="5"/>
       <c r="AA52" s="5"/>
       <c r="AB52" s="5"/>
       <c r="AC52" s="1">
-        <f t="shared" si="9"/>
-        <v>11.354750023301103</v>
-      </c>
-      <c r="AD52" s="1">
         <f t="shared" si="10"/>
         <v>11.354750023301103</v>
       </c>
+      <c r="AD52" s="1">
+        <f t="shared" si="11"/>
+        <v>11.354750023301103</v>
+      </c>
       <c r="AE52" s="1">
         <v>52.078800000000022</v>
       </c>
@@ -7222,18 +7371,21 @@
       </c>
       <c r="AM52" s="1"/>
       <c r="AN52" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO52" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP52" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR52" s="1"/>
       <c r="AS52" s="1"/>
       <c r="AT52" s="1"/>
@@ -7263,11 +7415,11 @@
       <c r="J53" s="13"/>
       <c r="K53" s="13"/>
       <c r="L53" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M53" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N53" s="13"/>
@@ -7284,25 +7436,25 @@
         <v>0</v>
       </c>
       <c r="W53" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X53" s="15"/>
       <c r="Y53" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z53" s="15"/>
       <c r="AA53" s="15"/>
       <c r="AB53" s="15"/>
       <c r="AC53" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD53" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD53" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE53" s="13">
         <v>0</v>
       </c>
@@ -7331,18 +7483,21 @@
         <v>61</v>
       </c>
       <c r="AN53" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO53" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP53" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ53" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR53" s="1"/>
       <c r="AS53" s="1"/>
       <c r="AT53" s="1"/>
@@ -7384,11 +7539,11 @@
         <v>744</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-144</v>
       </c>
       <c r="M54" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>420</v>
       </c>
       <c r="N54" s="1"/>
@@ -7407,15 +7562,15 @@
         <v>71.800000000000068</v>
       </c>
       <c r="W54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="X54" s="5">
-        <f t="shared" ref="X54:X55" si="23">11*W54-V54-U54-T54-S54-R54-Q54-O54-F54-AB54</f>
+        <f t="shared" ref="X54:X55" si="25">11*W54-V54-U54-T54-S54-R54-Q54-O54-F54-AB54</f>
         <v>331.19999999999993</v>
       </c>
       <c r="Y54" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>231.19999999999993</v>
       </c>
       <c r="Z54" s="5"/>
@@ -7424,11 +7579,11 @@
       </c>
       <c r="AB54" s="5"/>
       <c r="AC54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD54" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7.0571428571428578</v>
       </c>
       <c r="AE54" s="1">
@@ -7457,18 +7612,21 @@
       </c>
       <c r="AM54" s="1"/>
       <c r="AN54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>104</v>
       </c>
       <c r="AO54" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>45</v>
       </c>
-      <c r="AQ54" s="1"/>
+      <c r="AQ54" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR54" s="1"/>
       <c r="AS54" s="1"/>
       <c r="AT54" s="1"/>
@@ -7510,11 +7668,11 @@
         <v>898</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-157</v>
       </c>
       <c r="M55" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>741</v>
       </c>
       <c r="N55" s="1"/>
@@ -7531,15 +7689,15 @@
         <v>12.19999999999982</v>
       </c>
       <c r="W55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>148.19999999999999</v>
       </c>
       <c r="X55" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>906</v>
       </c>
       <c r="Y55" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>406</v>
       </c>
       <c r="Z55" s="5"/>
@@ -7548,11 +7706,11 @@
       </c>
       <c r="AB55" s="5"/>
       <c r="AC55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD55" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.8866396761133597</v>
       </c>
       <c r="AE55" s="1">
@@ -7581,18 +7739,21 @@
       </c>
       <c r="AM55" s="1"/>
       <c r="AN55" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>183</v>
       </c>
       <c r="AO55" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP55" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>225</v>
       </c>
-      <c r="AQ55" s="1"/>
+      <c r="AQ55" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR55" s="1"/>
       <c r="AS55" s="1"/>
       <c r="AT55" s="1"/>
@@ -7622,11 +7783,11 @@
       <c r="J56" s="13"/>
       <c r="K56" s="13"/>
       <c r="L56" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M56" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N56" s="13"/>
@@ -7643,25 +7804,25 @@
         <v>0</v>
       </c>
       <c r="W56" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X56" s="15"/>
       <c r="Y56" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z56" s="15"/>
       <c r="AA56" s="15"/>
       <c r="AB56" s="15"/>
       <c r="AC56" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD56" s="13" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AD56" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AE56" s="13">
         <v>0</v>
       </c>
@@ -7690,18 +7851,21 @@
         <v>61</v>
       </c>
       <c r="AN56" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO56" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP56" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ56" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ56" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR56" s="1"/>
       <c r="AS56" s="1"/>
       <c r="AT56" s="1"/>
@@ -7743,11 +7907,11 @@
         <v>47</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-19</v>
       </c>
       <c r="M57" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>28</v>
       </c>
       <c r="N57" s="1"/>
@@ -7764,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="W57" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.6</v>
       </c>
       <c r="X57" s="5">
@@ -7772,18 +7936,18 @@
         <v>32.019999999999996</v>
       </c>
       <c r="Y57" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>32.019999999999996</v>
       </c>
       <c r="Z57" s="5"/>
       <c r="AA57" s="5"/>
       <c r="AB57" s="5"/>
       <c r="AC57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="AD57" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.2821428571428575</v>
       </c>
       <c r="AE57" s="1">
@@ -7812,18 +7976,21 @@
       </c>
       <c r="AM57" s="1"/>
       <c r="AN57" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="AO57" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP57" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ57" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR57" s="1"/>
       <c r="AS57" s="1"/>
       <c r="AT57" s="1"/>
@@ -7865,11 +8032,11 @@
         <v>521.9</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-22.779999999999973</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>499.12</v>
       </c>
       <c r="N58" s="1"/>
@@ -7886,26 +8053,26 @@
         <v>157.58996399999981</v>
       </c>
       <c r="W58" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>99.823999999999998</v>
       </c>
       <c r="X58" s="5">
-        <f t="shared" ref="X58:X71" si="24">11*W58-V58-U58-T58-S58-R58-Q58-O58-F58-AB58</f>
+        <f t="shared" ref="X58:X71" si="26">11*W58-V58-U58-T58-S58-R58-Q58-O58-F58-AB58</f>
         <v>43.43853600000017</v>
       </c>
       <c r="Y58" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>43.43853600000017</v>
       </c>
       <c r="Z58" s="5"/>
       <c r="AA58" s="5"/>
       <c r="AB58" s="5"/>
       <c r="AC58" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11.000000000000002</v>
       </c>
       <c r="AD58" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.564848773841963</v>
       </c>
       <c r="AE58" s="1">
@@ -7934,18 +8101,21 @@
       </c>
       <c r="AM58" s="1"/>
       <c r="AN58" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>43</v>
       </c>
       <c r="AO58" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP58" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ58" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR58" s="1"/>
       <c r="AS58" s="1"/>
       <c r="AT58" s="1"/>
@@ -7987,11 +8157,11 @@
         <v>152</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-13</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>133</v>
       </c>
       <c r="N59" s="1"/>
@@ -8010,26 +8180,26 @@
         <v>0</v>
       </c>
       <c r="W59" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>26.6</v>
       </c>
       <c r="X59" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>118.60000000000002</v>
       </c>
       <c r="Y59" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>118.60000000000002</v>
       </c>
       <c r="Z59" s="5"/>
       <c r="AA59" s="5"/>
       <c r="AB59" s="5"/>
       <c r="AC59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD59" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.5413533834586461</v>
       </c>
       <c r="AE59" s="1">
@@ -8058,18 +8228,21 @@
       </c>
       <c r="AM59" s="1"/>
       <c r="AN59" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="AO59" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP59" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ59" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ59" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR59" s="1"/>
       <c r="AS59" s="1"/>
       <c r="AT59" s="1"/>
@@ -8111,11 +8284,11 @@
         <v>565.73599999999999</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-2.1399999999999864</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>510.16</v>
       </c>
       <c r="N60" s="1">
@@ -8134,7 +8307,7 @@
         <v>61.587421999999961</v>
       </c>
       <c r="W60" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>102.03200000000001</v>
       </c>
       <c r="X60" s="5">
@@ -8142,18 +8315,18 @@
         <v>650.53757800000017</v>
       </c>
       <c r="Y60" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>650.53757800000017</v>
       </c>
       <c r="Z60" s="5"/>
       <c r="AA60" s="5"/>
       <c r="AB60" s="5"/>
       <c r="AC60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="AD60" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.62418086482672</v>
       </c>
       <c r="AE60" s="1">
@@ -8182,18 +8355,21 @@
       </c>
       <c r="AM60" s="1"/>
       <c r="AN60" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>651</v>
       </c>
       <c r="AO60" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP60" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ60" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR60" s="1"/>
       <c r="AS60" s="1"/>
       <c r="AT60" s="1"/>
@@ -8235,11 +8411,11 @@
         <v>41.8</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.11400000000000432</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>41.914000000000001</v>
       </c>
       <c r="N61" s="1"/>
@@ -8256,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.3827999999999996</v>
       </c>
       <c r="X61" s="5">
@@ -8264,18 +8440,18 @@
         <v>51.130200000000002</v>
       </c>
       <c r="Y61" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51.130200000000002</v>
       </c>
       <c r="Z61" s="5"/>
       <c r="AA61" s="5"/>
       <c r="AB61" s="5"/>
       <c r="AC61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="AD61" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.9005821443908961</v>
       </c>
       <c r="AE61" s="1">
@@ -8304,18 +8480,21 @@
       </c>
       <c r="AM61" s="1"/>
       <c r="AN61" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>51</v>
       </c>
       <c r="AO61" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP61" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ61" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR61" s="1"/>
       <c r="AS61" s="1"/>
       <c r="AT61" s="1"/>
@@ -8357,11 +8536,11 @@
         <v>135</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-8</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>121</v>
       </c>
       <c r="N62" s="1"/>
@@ -8380,26 +8559,26 @@
         <v>0</v>
       </c>
       <c r="W62" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>24.2</v>
       </c>
       <c r="X62" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>112.19999999999999</v>
       </c>
       <c r="Y62" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>112.19999999999999</v>
       </c>
       <c r="Z62" s="5"/>
       <c r="AA62" s="5"/>
       <c r="AB62" s="5"/>
       <c r="AC62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD62" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.3636363636363642</v>
       </c>
       <c r="AE62" s="1">
@@ -8428,18 +8607,21 @@
       </c>
       <c r="AM62" s="1"/>
       <c r="AN62" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11</v>
       </c>
       <c r="AO62" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP62" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ62" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ62" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR62" s="1"/>
       <c r="AS62" s="1"/>
       <c r="AT62" s="1"/>
@@ -8481,11 +8663,11 @@
         <v>20</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-12</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>8</v>
       </c>
       <c r="N63" s="1"/>
@@ -8502,25 +8684,25 @@
         <v>17.599999999999991</v>
       </c>
       <c r="W63" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
       <c r="X63" s="5"/>
       <c r="Y63" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z63" s="5"/>
       <c r="AA63" s="5"/>
       <c r="AB63" s="5"/>
       <c r="AC63" s="1">
-        <f t="shared" si="9"/>
-        <v>20.999999999999996</v>
-      </c>
-      <c r="AD63" s="1">
         <f t="shared" si="10"/>
         <v>20.999999999999996</v>
       </c>
+      <c r="AD63" s="1">
+        <f t="shared" si="11"/>
+        <v>20.999999999999996</v>
+      </c>
       <c r="AE63" s="1">
         <v>2.8</v>
       </c>
@@ -8547,18 +8729,21 @@
       </c>
       <c r="AM63" s="1"/>
       <c r="AN63" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO63" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP63" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ63" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR63" s="1"/>
       <c r="AS63" s="1"/>
       <c r="AT63" s="1"/>
@@ -8600,11 +8785,11 @@
         <v>70</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-32.805999999999997</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>37.194000000000003</v>
       </c>
       <c r="N64" s="1"/>
@@ -8621,25 +8806,25 @@
         <v>0</v>
       </c>
       <c r="W64" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.4388000000000005</v>
       </c>
       <c r="X64" s="5"/>
       <c r="Y64" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z64" s="5"/>
       <c r="AA64" s="5"/>
       <c r="AB64" s="5"/>
       <c r="AC64" s="1">
-        <f t="shared" si="9"/>
-        <v>13.39731677152229</v>
-      </c>
-      <c r="AD64" s="1">
         <f t="shared" si="10"/>
         <v>13.39731677152229</v>
       </c>
+      <c r="AD64" s="1">
+        <f t="shared" si="11"/>
+        <v>13.39731677152229</v>
+      </c>
       <c r="AE64" s="1">
         <v>8.8168000000000006</v>
       </c>
@@ -8666,18 +8851,21 @@
       </c>
       <c r="AM64" s="1"/>
       <c r="AN64" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO64" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP64" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ64" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR64" s="1"/>
       <c r="AS64" s="1"/>
       <c r="AT64" s="1"/>
@@ -8719,11 +8907,11 @@
         <v>67.099999999999994</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-26.799999999999997</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>40.299999999999997</v>
       </c>
       <c r="N65" s="1"/>
@@ -8740,26 +8928,26 @@
         <v>44.187800000000003</v>
       </c>
       <c r="W65" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.0599999999999987</v>
       </c>
       <c r="X65" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>43.06019999999998</v>
       </c>
       <c r="Y65" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>43.06019999999998</v>
       </c>
       <c r="Z65" s="5"/>
       <c r="AA65" s="5"/>
       <c r="AB65" s="5"/>
       <c r="AC65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD65" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.6575434243176188</v>
       </c>
       <c r="AE65" s="1">
@@ -8788,18 +8976,21 @@
       </c>
       <c r="AM65" s="1"/>
       <c r="AN65" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>43</v>
       </c>
       <c r="AO65" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP65" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ65" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR65" s="1"/>
       <c r="AS65" s="1"/>
       <c r="AT65" s="1"/>
@@ -8841,11 +9032,11 @@
         <v>655</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-181</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>474</v>
       </c>
       <c r="N66" s="1"/>
@@ -8862,26 +9053,26 @@
         <v>602.85199999999952</v>
       </c>
       <c r="W66" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>94.8</v>
       </c>
       <c r="X66" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>188.46800000000002</v>
       </c>
       <c r="Y66" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>188.46800000000002</v>
       </c>
       <c r="Z66" s="5"/>
       <c r="AA66" s="5"/>
       <c r="AB66" s="5"/>
       <c r="AC66" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD66" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.0119409282700413</v>
       </c>
       <c r="AE66" s="1">
@@ -8910,18 +9101,21 @@
       </c>
       <c r="AM66" s="1"/>
       <c r="AN66" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>75</v>
       </c>
       <c r="AO66" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP66" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ66" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ66" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR66" s="1"/>
       <c r="AS66" s="1"/>
       <c r="AT66" s="1"/>
@@ -8963,11 +9157,11 @@
         <v>552</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-73</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>479</v>
       </c>
       <c r="N67" s="1"/>
@@ -8988,14 +9182,14 @@
         <v>206.33683671519981</v>
       </c>
       <c r="W67" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>95.8</v>
       </c>
       <c r="X67" s="5">
         <v>200</v>
       </c>
       <c r="Y67" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>200</v>
       </c>
       <c r="Z67" s="5"/>
@@ -9004,11 +9198,11 @@
         <v>600</v>
       </c>
       <c r="AC67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.3559916492693134</v>
       </c>
       <c r="AD67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.2609603340306142E-3</v>
       </c>
       <c r="AE67" s="1">
@@ -9037,18 +9231,21 @@
       </c>
       <c r="AM67" s="1"/>
       <c r="AN67" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>80</v>
       </c>
       <c r="AO67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP67" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ67" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ67" s="1">
+        <f t="shared" si="15"/>
+        <v>240</v>
+      </c>
       <c r="AR67" s="1"/>
       <c r="AS67" s="1"/>
       <c r="AT67" s="1"/>
@@ -9090,11 +9287,11 @@
         <v>56.319000000000003</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3.3069999999999951</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>59.625999999999998</v>
       </c>
       <c r="N68" s="1"/>
@@ -9111,26 +9308,26 @@
         <v>0</v>
       </c>
       <c r="W68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11.9252</v>
       </c>
       <c r="X68" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>67.822200000000009</v>
       </c>
       <c r="Y68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>67.822200000000009</v>
       </c>
       <c r="Z68" s="5"/>
       <c r="AA68" s="5"/>
       <c r="AB68" s="5"/>
       <c r="AC68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="AD68" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.3126991580853984</v>
       </c>
       <c r="AE68" s="1">
@@ -9159,18 +9356,21 @@
       </c>
       <c r="AM68" s="1"/>
       <c r="AN68" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>68</v>
       </c>
       <c r="AO68" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP68" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ68" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR68" s="1"/>
       <c r="AS68" s="1"/>
       <c r="AT68" s="1"/>
@@ -9212,11 +9412,11 @@
         <v>105.61</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3.7390000000000043</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>109.349</v>
       </c>
       <c r="N69" s="1"/>
@@ -9233,7 +9433,7 @@
         <v>4.5566399999999447</v>
       </c>
       <c r="W69" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>21.869800000000001</v>
       </c>
       <c r="X69" s="5">
@@ -9241,18 +9441,18 @@
         <v>133.93400000000005</v>
       </c>
       <c r="Y69" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>133.93400000000005</v>
       </c>
       <c r="Z69" s="5"/>
       <c r="AA69" s="5"/>
       <c r="AB69" s="5"/>
       <c r="AC69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10.000000000000002</v>
       </c>
       <c r="AD69" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.8758470585007618</v>
       </c>
       <c r="AE69" s="1">
@@ -9281,18 +9481,21 @@
       </c>
       <c r="AM69" s="1"/>
       <c r="AN69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>134</v>
       </c>
       <c r="AO69" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP69" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ69" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR69" s="1"/>
       <c r="AS69" s="1"/>
       <c r="AT69" s="1"/>
@@ -9334,11 +9537,11 @@
         <v>587.30999999999995</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="25">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="27">E70-K70</f>
         <v>9.9150000000000773</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" ref="M70:M101" si="26">E70-N70+P70</f>
+        <f t="shared" ref="M70:M101" si="28">E70-N70+P70</f>
         <v>597.22500000000002</v>
       </c>
       <c r="N70" s="1"/>
@@ -9355,25 +9558,25 @@
         <v>49.546219999999721</v>
       </c>
       <c r="W70" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>119.44500000000001</v>
       </c>
       <c r="X70" s="5"/>
       <c r="Y70" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z70" s="5"/>
       <c r="AA70" s="5"/>
       <c r="AB70" s="5"/>
       <c r="AC70" s="1">
-        <f t="shared" si="9"/>
-        <v>12.408539495165137</v>
-      </c>
-      <c r="AD70" s="1">
         <f t="shared" si="10"/>
         <v>12.408539495165137</v>
       </c>
+      <c r="AD70" s="1">
+        <f t="shared" si="11"/>
+        <v>12.408539495165137</v>
+      </c>
       <c r="AE70" s="1">
         <v>150.35599999999999</v>
       </c>
@@ -9400,18 +9603,21 @@
       </c>
       <c r="AM70" s="1"/>
       <c r="AN70" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO70" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AP70" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ70" s="1"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AR70" s="1"/>
       <c r="AS70" s="1"/>
       <c r="AT70" s="1"/>
@@ -9453,11 +9659,11 @@
         <v>60.61</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-9.7789999999999964</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>50.831000000000003</v>
       </c>
       <c r="N71" s="1"/>
@@ -9474,26 +9680,26 @@
         <v>0</v>
       </c>
       <c r="W71" s="1">
-        <f t="shared" ref="W71:W134" si="27">M71/5</f>
+        <f t="shared" ref="W71:W134" si="29">M71/5</f>
         <v>10.1662</v>
       </c>
       <c r="X71" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>20.392199999999988</v>
       </c>
       <c r="Y71" s="5">
-        <f t="shared" ref="Y71:Y134" si="28">X71-Z71-AA71</f>
+        <f t="shared" ref="Y71:Y134" si="30">X71-Z71-AA71</f>
         <v>20.392199999999988</v>
       </c>
       <c r="Z71" s="5"/>
       <c r="AA71" s="5"/>
       <c r="AB71" s="5"/>
       <c r="AC71" s="1">
-        <f t="shared" ref="AC71:AC134" si="29">(F71+O71+Q71+R71+S71+T71+U71+V71+X71+AB71)/W71</f>
+        <f t="shared" ref="AC71:AC134" si="31">(F71+O71+Q71+R71+S71+T71+U71+V71+X71+AB71)/W71</f>
         <v>11</v>
       </c>
       <c r="AD71" s="1">
-        <f t="shared" ref="AD71:AD134" si="30">(F71+O71+Q71+R71+S71+T71+U71+V71)/W71</f>
+        <f t="shared" ref="AD71:AD134" si="32">(F71+O71+Q71+R71+S71+T71+U71+V71)/W71</f>
         <v>8.9941177627825546</v>
       </c>
       <c r="AE71" s="1">
@@ -9522,18 +9728,21 @@
       </c>
       <c r="AM71" s="1"/>
       <c r="AN71" s="1">
-        <f t="shared" ref="AN71:AN134" si="31">ROUND(G71*Y71,0)</f>
+        <f t="shared" ref="AN71:AN134" si="33">ROUND(G71*Y71,0)</f>
         <v>20</v>
       </c>
       <c r="AO71" s="1">
-        <f t="shared" ref="AO71:AO134" si="32">ROUND(G71*Z71,0)</f>
+        <f t="shared" ref="AO71:AO134" si="34">ROUND(G71*Z71,0)</f>
         <v>0</v>
       </c>
       <c r="AP71" s="1">
-        <f t="shared" ref="AP71:AP134" si="33">ROUND(G71*AA71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ71" s="1"/>
+        <f t="shared" ref="AP71:AQ134" si="35">ROUND(G71*AA71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="1">
+        <f t="shared" ref="AQ71:AQ134" si="36">ROUND(G71*AB71,0)</f>
+        <v>0</v>
+      </c>
       <c r="AR71" s="1"/>
       <c r="AS71" s="1"/>
       <c r="AT71" s="1"/>
@@ -9563,11 +9772,11 @@
       <c r="J72" s="13"/>
       <c r="K72" s="13"/>
       <c r="L72" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M72" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N72" s="13"/>
@@ -9584,23 +9793,23 @@
         <v>0</v>
       </c>
       <c r="W72" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X72" s="15"/>
       <c r="Y72" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z72" s="15"/>
       <c r="AA72" s="15"/>
       <c r="AB72" s="15"/>
       <c r="AC72" s="13" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD72" s="13" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE72" s="13">
@@ -9631,18 +9840,21 @@
         <v>61</v>
       </c>
       <c r="AN72" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO72" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP72" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ72" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ72" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR72" s="1"/>
       <c r="AS72" s="1"/>
       <c r="AT72" s="1"/>
@@ -9684,11 +9896,11 @@
         <v>528.12</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-62.951000000000022</v>
       </c>
       <c r="M73" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>389.149</v>
       </c>
       <c r="N73" s="1"/>
@@ -9707,26 +9919,26 @@
         <v>0</v>
       </c>
       <c r="W73" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>77.829800000000006</v>
       </c>
       <c r="X73" s="5">
-        <f t="shared" ref="X73" si="34">11*W73-V73-U73-T73-S73-R73-Q73-O73-F73-AB73</f>
+        <f t="shared" ref="X73" si="37">11*W73-V73-U73-T73-S73-R73-Q73-O73-F73-AB73</f>
         <v>119.35780000000011</v>
       </c>
       <c r="Y73" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>119.35780000000011</v>
       </c>
       <c r="Z73" s="5"/>
       <c r="AA73" s="5"/>
       <c r="AB73" s="5"/>
       <c r="AC73" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD73" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>9.4664254565731891</v>
       </c>
       <c r="AE73" s="1">
@@ -9755,18 +9967,21 @@
       </c>
       <c r="AM73" s="1"/>
       <c r="AN73" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>119</v>
       </c>
       <c r="AO73" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP73" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ73" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR73" s="1"/>
       <c r="AS73" s="1"/>
       <c r="AT73" s="1"/>
@@ -9808,11 +10023,11 @@
         <v>1308</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-375</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>661</v>
       </c>
       <c r="N74" s="1"/>
@@ -9831,7 +10046,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>132.19999999999999</v>
       </c>
       <c r="X74" s="5">
@@ -9839,7 +10054,7 @@
         <v>772.8</v>
       </c>
       <c r="Y74" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>272.79999999999995</v>
       </c>
       <c r="Z74" s="5"/>
@@ -9848,11 +10063,11 @@
       </c>
       <c r="AB74" s="5"/>
       <c r="AC74" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="AD74" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.1543116490166416</v>
       </c>
       <c r="AE74" s="1">
@@ -9881,18 +10096,21 @@
       </c>
       <c r="AM74" s="1"/>
       <c r="AN74" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>164</v>
       </c>
       <c r="AO74" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP74" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>300</v>
       </c>
-      <c r="AQ74" s="1"/>
+      <c r="AQ74" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR74" s="1"/>
       <c r="AS74" s="1"/>
       <c r="AT74" s="1"/>
@@ -9934,11 +10152,11 @@
         <v>1054</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-189</v>
       </c>
       <c r="M75" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>593</v>
       </c>
       <c r="N75" s="1"/>
@@ -9957,7 +10175,7 @@
         <v>159.9440000000001</v>
       </c>
       <c r="W75" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>118.6</v>
       </c>
       <c r="X75" s="5">
@@ -9965,7 +10183,7 @@
         <v>684.05599999999981</v>
       </c>
       <c r="Y75" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>384.05599999999981</v>
       </c>
       <c r="Z75" s="5"/>
@@ -9974,11 +10192,11 @@
       </c>
       <c r="AB75" s="5"/>
       <c r="AC75" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD75" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.2322428330522772</v>
       </c>
       <c r="AE75" s="1">
@@ -10007,18 +10225,21 @@
       </c>
       <c r="AM75" s="1"/>
       <c r="AN75" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>230</v>
       </c>
       <c r="AO75" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP75" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>180</v>
       </c>
-      <c r="AQ75" s="1"/>
+      <c r="AQ75" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR75" s="1"/>
       <c r="AS75" s="1"/>
       <c r="AT75" s="1"/>
@@ -10048,11 +10269,11 @@
       <c r="J76" s="13"/>
       <c r="K76" s="13"/>
       <c r="L76" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M76" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N76" s="13"/>
@@ -10069,23 +10290,23 @@
         <v>0</v>
       </c>
       <c r="W76" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X76" s="15"/>
       <c r="Y76" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z76" s="15"/>
       <c r="AA76" s="15"/>
       <c r="AB76" s="15"/>
       <c r="AC76" s="13" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD76" s="13" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE76" s="13">
@@ -10116,18 +10337,21 @@
         <v>61</v>
       </c>
       <c r="AN76" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO76" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP76" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ76" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ76" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR76" s="1"/>
       <c r="AS76" s="1"/>
       <c r="AT76" s="1"/>
@@ -10161,11 +10385,11 @@
       <c r="J77" s="13"/>
       <c r="K77" s="13"/>
       <c r="L77" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M77" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N77" s="13"/>
@@ -10182,23 +10406,23 @@
         <v>0</v>
       </c>
       <c r="W77" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X77" s="15"/>
       <c r="Y77" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z77" s="15"/>
       <c r="AA77" s="15"/>
       <c r="AB77" s="15"/>
       <c r="AC77" s="13" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD77" s="13" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE77" s="13">
@@ -10229,18 +10453,21 @@
         <v>61</v>
       </c>
       <c r="AN77" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO77" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP77" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ77" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR77" s="1"/>
       <c r="AS77" s="1"/>
       <c r="AT77" s="1"/>
@@ -10282,11 +10509,11 @@
         <v>60</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-13</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>47</v>
       </c>
       <c r="N78" s="1"/>
@@ -10303,23 +10530,23 @@
         <v>0</v>
       </c>
       <c r="W78" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9.4</v>
       </c>
       <c r="X78" s="5"/>
       <c r="Y78" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z78" s="5"/>
       <c r="AA78" s="5"/>
       <c r="AB78" s="5"/>
       <c r="AC78" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>12.659574468085106</v>
       </c>
       <c r="AD78" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>12.659574468085106</v>
       </c>
       <c r="AE78" s="1">
@@ -10348,18 +10575,21 @@
       </c>
       <c r="AM78" s="1"/>
       <c r="AN78" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO78" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP78" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ78" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ78" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR78" s="1"/>
       <c r="AS78" s="1"/>
       <c r="AT78" s="1"/>
@@ -10401,11 +10631,11 @@
         <v>207</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-63</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>144</v>
       </c>
       <c r="N79" s="1"/>
@@ -10422,26 +10652,26 @@
         <v>0</v>
       </c>
       <c r="W79" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>28.8</v>
       </c>
       <c r="X79" s="5">
-        <f t="shared" ref="X79:X85" si="35">11*W79-V79-U79-T79-S79-R79-Q79-O79-F79-AB79</f>
+        <f t="shared" ref="X79:X85" si="38">11*W79-V79-U79-T79-S79-R79-Q79-O79-F79-AB79</f>
         <v>62.560000000000116</v>
       </c>
       <c r="Y79" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>62.560000000000116</v>
       </c>
       <c r="Z79" s="5"/>
       <c r="AA79" s="5"/>
       <c r="AB79" s="5"/>
       <c r="AC79" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11.000000000000002</v>
       </c>
       <c r="AD79" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8.8277777777777757</v>
       </c>
       <c r="AE79" s="1">
@@ -10470,18 +10700,21 @@
       </c>
       <c r="AM79" s="1"/>
       <c r="AN79" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>23</v>
       </c>
       <c r="AO79" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP79" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ79" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ79" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR79" s="1"/>
       <c r="AS79" s="1"/>
       <c r="AT79" s="1"/>
@@ -10523,11 +10756,11 @@
         <v>1355</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-685</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>670</v>
       </c>
       <c r="N80" s="1"/>
@@ -10544,25 +10777,25 @@
         <v>0</v>
       </c>
       <c r="W80" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>134</v>
       </c>
       <c r="X80" s="5">
         <v>100</v>
       </c>
       <c r="Y80" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>100</v>
       </c>
       <c r="Z80" s="5"/>
       <c r="AA80" s="5"/>
       <c r="AB80" s="5"/>
       <c r="AC80" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4.3283582089552235</v>
       </c>
       <c r="AD80" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.5820895522388061</v>
       </c>
       <c r="AE80" s="1">
@@ -10593,18 +10826,21 @@
         <v>189</v>
       </c>
       <c r="AN80" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>60</v>
       </c>
       <c r="AO80" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP80" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ80" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ80" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR80" s="1"/>
       <c r="AS80" s="1"/>
       <c r="AT80" s="1"/>
@@ -10646,11 +10882,11 @@
         <v>391</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-172</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>219</v>
       </c>
       <c r="N81" s="1"/>
@@ -10667,15 +10903,15 @@
         <v>0</v>
       </c>
       <c r="W81" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>43.8</v>
       </c>
       <c r="X81" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>232.14</v>
       </c>
       <c r="Y81" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>132.13999999999999</v>
       </c>
       <c r="Z81" s="5"/>
@@ -10684,11 +10920,11 @@
       </c>
       <c r="AB81" s="5"/>
       <c r="AC81" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD81" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.7</v>
       </c>
       <c r="AE81" s="1">
@@ -10717,18 +10953,21 @@
       </c>
       <c r="AM81" s="1"/>
       <c r="AN81" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>44</v>
       </c>
       <c r="AO81" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP81" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>33</v>
       </c>
-      <c r="AQ81" s="1"/>
+      <c r="AQ81" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR81" s="1"/>
       <c r="AS81" s="1"/>
       <c r="AT81" s="1"/>
@@ -10770,11 +11009,11 @@
         <v>61</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-19</v>
       </c>
       <c r="M82" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>42</v>
       </c>
       <c r="N82" s="1"/>
@@ -10791,23 +11030,23 @@
         <v>0</v>
       </c>
       <c r="W82" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8.4</v>
       </c>
       <c r="X82" s="5"/>
       <c r="Y82" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z82" s="5"/>
       <c r="AA82" s="5"/>
       <c r="AB82" s="5"/>
       <c r="AC82" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>13.666666666666668</v>
       </c>
       <c r="AD82" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>13.666666666666668</v>
       </c>
       <c r="AE82" s="1">
@@ -10836,18 +11075,21 @@
       </c>
       <c r="AM82" s="1"/>
       <c r="AN82" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO82" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP82" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ82" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ82" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR82" s="1"/>
       <c r="AS82" s="1"/>
       <c r="AT82" s="1"/>
@@ -10889,11 +11131,11 @@
         <v>208</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-77</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>131</v>
       </c>
       <c r="N83" s="1"/>
@@ -10914,14 +11156,14 @@
         <v>16.159999999999972</v>
       </c>
       <c r="W83" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>26.2</v>
       </c>
       <c r="X83" s="5">
         <v>50</v>
       </c>
       <c r="Y83" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>50</v>
       </c>
       <c r="Z83" s="5"/>
@@ -10930,11 +11172,11 @@
         <v>250</v>
       </c>
       <c r="AC83" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11.053435114503811</v>
       </c>
       <c r="AD83" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-0.39694656488550167</v>
       </c>
       <c r="AE83" s="1">
@@ -10963,18 +11205,21 @@
       </c>
       <c r="AM83" s="1"/>
       <c r="AN83" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>18</v>
       </c>
       <c r="AO83" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP83" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ83" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ83" s="1">
+        <f t="shared" si="36"/>
+        <v>88</v>
+      </c>
       <c r="AR83" s="1"/>
       <c r="AS83" s="1"/>
       <c r="AT83" s="1"/>
@@ -11014,11 +11259,11 @@
         <v>650</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-317</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>333</v>
       </c>
       <c r="N84" s="1"/>
@@ -11037,15 +11282,15 @@
         <v>391.79</v>
       </c>
       <c r="W84" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>66.599999999999994</v>
       </c>
       <c r="X84" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>344.12714285714281</v>
       </c>
       <c r="Y84" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>244.12714285714281</v>
       </c>
       <c r="Z84" s="5"/>
@@ -11054,11 +11299,11 @@
       </c>
       <c r="AB84" s="5"/>
       <c r="AC84" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD84" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.8329257829257832</v>
       </c>
       <c r="AE84" s="1">
@@ -11087,18 +11332,21 @@
       </c>
       <c r="AM84" s="1"/>
       <c r="AN84" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>85</v>
       </c>
       <c r="AO84" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP84" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>35</v>
       </c>
-      <c r="AQ84" s="1"/>
+      <c r="AQ84" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR84" s="1"/>
       <c r="AS84" s="1"/>
       <c r="AT84" s="1"/>
@@ -11140,11 +11388,11 @@
         <v>24</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>20</v>
       </c>
       <c r="N85" s="1"/>
@@ -11163,26 +11411,26 @@
         <v>0</v>
       </c>
       <c r="W85" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="X85" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>8</v>
       </c>
       <c r="Y85" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="Z85" s="5"/>
       <c r="AA85" s="5"/>
       <c r="AB85" s="5"/>
       <c r="AC85" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD85" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>9</v>
       </c>
       <c r="AE85" s="1">
@@ -11211,18 +11459,21 @@
       </c>
       <c r="AM85" s="1"/>
       <c r="AN85" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3</v>
       </c>
       <c r="AO85" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP85" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ85" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR85" s="1"/>
       <c r="AS85" s="1"/>
       <c r="AT85" s="1"/>
@@ -11262,11 +11513,11 @@
         <v>7.6</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.1240000000000006</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>8.7240000000000002</v>
       </c>
       <c r="N86" s="1"/>
@@ -11283,23 +11534,23 @@
         <v>0</v>
       </c>
       <c r="W86" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.7448000000000001</v>
       </c>
       <c r="X86" s="5"/>
       <c r="Y86" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z86" s="5"/>
       <c r="AA86" s="5"/>
       <c r="AB86" s="5"/>
       <c r="AC86" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>29.959880788629068</v>
       </c>
       <c r="AD86" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>29.959880788629068</v>
       </c>
       <c r="AE86" s="1">
@@ -11330,18 +11581,21 @@
         <v>52</v>
       </c>
       <c r="AN86" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO86" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP86" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ86" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR86" s="1"/>
       <c r="AS86" s="1"/>
       <c r="AT86" s="1"/>
@@ -11371,11 +11625,11 @@
       <c r="J87" s="13"/>
       <c r="K87" s="13"/>
       <c r="L87" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M87" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N87" s="13"/>
@@ -11392,23 +11646,23 @@
         <v>0</v>
       </c>
       <c r="W87" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X87" s="15"/>
       <c r="Y87" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z87" s="15"/>
       <c r="AA87" s="15"/>
       <c r="AB87" s="15"/>
       <c r="AC87" s="13" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD87" s="13" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE87" s="13">
@@ -11439,18 +11693,21 @@
         <v>61</v>
       </c>
       <c r="AN87" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO87" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP87" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ87" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR87" s="1"/>
       <c r="AS87" s="1"/>
       <c r="AT87" s="1"/>
@@ -11492,11 +11749,11 @@
         <v>5332.04</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-285.67299999999977</v>
       </c>
       <c r="M88" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3155.9270000000006</v>
       </c>
       <c r="N88" s="1">
@@ -11517,15 +11774,15 @@
         <v>1014.838891999999</v>
       </c>
       <c r="W88" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>631.18540000000007</v>
       </c>
       <c r="X88" s="5">
-        <f t="shared" ref="X88" si="36">11*W88-V88-U88-T88-S88-R88-Q88-O88-F88-AB88</f>
+        <f t="shared" ref="X88" si="39">11*W88-V88-U88-T88-S88-R88-Q88-O88-F88-AB88</f>
         <v>3745.7275080000018</v>
       </c>
       <c r="Y88" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1445.7275080000018</v>
       </c>
       <c r="Z88" s="5"/>
@@ -11534,11 +11791,11 @@
       </c>
       <c r="AB88" s="5"/>
       <c r="AC88" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD88" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.0655669348498851</v>
       </c>
       <c r="AE88" s="1">
@@ -11567,18 +11824,21 @@
       </c>
       <c r="AM88" s="1"/>
       <c r="AN88" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1446</v>
       </c>
       <c r="AO88" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP88" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>2300</v>
       </c>
-      <c r="AQ88" s="1"/>
+      <c r="AQ88" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR88" s="1"/>
       <c r="AS88" s="1"/>
       <c r="AT88" s="1"/>
@@ -11620,11 +11880,11 @@
         <v>419</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-85</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>272</v>
       </c>
       <c r="N89" s="1"/>
@@ -11643,15 +11903,15 @@
         <v>79.222000000000037</v>
       </c>
       <c r="W89" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>54.4</v>
       </c>
       <c r="X89" s="5">
-        <f t="shared" ref="X89:X90" si="37">10*W89-V89-U89-T89-S89-R89-Q89-O89-F89-AB89</f>
+        <f t="shared" ref="X89:X90" si="40">10*W89-V89-U89-T89-S89-R89-Q89-O89-F89-AB89</f>
         <v>350.77799999999996</v>
       </c>
       <c r="Y89" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>150.77799999999996</v>
       </c>
       <c r="Z89" s="5"/>
@@ -11660,11 +11920,11 @@
       </c>
       <c r="AB89" s="5"/>
       <c r="AC89" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD89" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.5518750000000008</v>
       </c>
       <c r="AE89" s="1">
@@ -11693,18 +11953,21 @@
       </c>
       <c r="AM89" s="1"/>
       <c r="AN89" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>45</v>
       </c>
       <c r="AO89" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP89" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>60</v>
       </c>
-      <c r="AQ89" s="1"/>
+      <c r="AQ89" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR89" s="1"/>
       <c r="AS89" s="1"/>
       <c r="AT89" s="1"/>
@@ -11746,11 +12009,11 @@
         <v>2077.1579999999999</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-246.34699999999998</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1308.8530000000001</v>
       </c>
       <c r="N90" s="1">
@@ -11769,15 +12032,15 @@
         <v>354.90731280000023</v>
       </c>
       <c r="W90" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>261.7706</v>
       </c>
       <c r="X90" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1470.8196780000007</v>
       </c>
       <c r="Y90" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>570.81967800000075</v>
       </c>
       <c r="Z90" s="5"/>
@@ -11786,11 +12049,11 @@
       </c>
       <c r="AB90" s="5"/>
       <c r="AC90" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD90" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.3812648250032646</v>
       </c>
       <c r="AE90" s="1">
@@ -11819,18 +12082,21 @@
       </c>
       <c r="AM90" s="1"/>
       <c r="AN90" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>571</v>
       </c>
       <c r="AO90" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP90" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>900</v>
       </c>
-      <c r="AQ90" s="1"/>
+      <c r="AQ90" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR90" s="1"/>
       <c r="AS90" s="1"/>
       <c r="AT90" s="1"/>
@@ -11872,11 +12138,11 @@
         <v>3383.4009999999998</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-282.80899999999974</v>
       </c>
       <c r="M91" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>2572.6910000000003</v>
       </c>
       <c r="N91" s="1">
@@ -11897,23 +12163,23 @@
         <v>0</v>
       </c>
       <c r="W91" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>514.53820000000007</v>
       </c>
       <c r="X91" s="5"/>
       <c r="Y91" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z91" s="5"/>
       <c r="AA91" s="5"/>
       <c r="AB91" s="5"/>
       <c r="AC91" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>14.122642400505928</v>
       </c>
       <c r="AD91" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.122642400505928</v>
       </c>
       <c r="AE91" s="1">
@@ -11942,18 +12208,21 @@
       </c>
       <c r="AM91" s="1"/>
       <c r="AN91" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO91" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP91" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ91" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ91" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR91" s="1"/>
       <c r="AS91" s="1"/>
       <c r="AT91" s="1"/>
@@ -11995,11 +12264,11 @@
         <v>7387.1009999999997</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-400.41499999999996</v>
       </c>
       <c r="M92" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3289.4849999999992</v>
       </c>
       <c r="N92" s="1">
@@ -12024,23 +12293,23 @@
         <v>0</v>
       </c>
       <c r="W92" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>657.89699999999982</v>
       </c>
       <c r="X92" s="5"/>
       <c r="Y92" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z92" s="5"/>
       <c r="AA92" s="5"/>
       <c r="AB92" s="5"/>
       <c r="AC92" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>14.051141744072403</v>
       </c>
       <c r="AD92" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14.051141744072403</v>
       </c>
       <c r="AE92" s="1">
@@ -12069,18 +12338,21 @@
       </c>
       <c r="AM92" s="1"/>
       <c r="AN92" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO92" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP92" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ92" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR92" s="1"/>
       <c r="AS92" s="1"/>
       <c r="AT92" s="1"/>
@@ -12120,11 +12392,11 @@
         <v>15</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-0.18699999999999939</v>
       </c>
       <c r="M93" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>14.813000000000001</v>
       </c>
       <c r="N93" s="1"/>
@@ -12141,23 +12413,23 @@
         <v>0</v>
       </c>
       <c r="W93" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.9626000000000001</v>
       </c>
       <c r="X93" s="5"/>
       <c r="Y93" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z93" s="5"/>
       <c r="AA93" s="5"/>
       <c r="AB93" s="5"/>
       <c r="AC93" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>34.758090866131113</v>
       </c>
       <c r="AD93" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>34.758090866131113</v>
       </c>
       <c r="AE93" s="1">
@@ -12186,18 +12458,21 @@
       </c>
       <c r="AM93" s="1"/>
       <c r="AN93" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO93" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP93" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ93" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR93" s="1"/>
       <c r="AS93" s="1"/>
       <c r="AT93" s="1"/>
@@ -12231,11 +12506,11 @@
       <c r="J94" s="13"/>
       <c r="K94" s="13"/>
       <c r="L94" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M94" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N94" s="13"/>
@@ -12252,23 +12527,23 @@
         <v>0</v>
       </c>
       <c r="W94" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X94" s="15"/>
       <c r="Y94" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z94" s="15"/>
       <c r="AA94" s="15"/>
       <c r="AB94" s="15"/>
       <c r="AC94" s="13" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD94" s="13" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE94" s="13">
@@ -12297,18 +12572,21 @@
       </c>
       <c r="AM94" s="13"/>
       <c r="AN94" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO94" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP94" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ94" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ94" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR94" s="1"/>
       <c r="AS94" s="1"/>
       <c r="AT94" s="1"/>
@@ -12348,11 +12626,11 @@
         <v>28.3</v>
       </c>
       <c r="L95" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-8.7980000000000018</v>
       </c>
       <c r="M95" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>19.501999999999999</v>
       </c>
       <c r="N95" s="13"/>
@@ -12369,23 +12647,23 @@
         <v>0</v>
       </c>
       <c r="W95" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>3.9003999999999999</v>
       </c>
       <c r="X95" s="15"/>
       <c r="Y95" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z95" s="15"/>
       <c r="AA95" s="15"/>
       <c r="AB95" s="15"/>
       <c r="AC95" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>139.72207978668854</v>
       </c>
       <c r="AD95" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>139.72207978668854</v>
       </c>
       <c r="AE95" s="13">
@@ -12416,18 +12694,21 @@
         <v>52</v>
       </c>
       <c r="AN95" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO95" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP95" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ95" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ95" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR95" s="1"/>
       <c r="AS95" s="1"/>
       <c r="AT95" s="1"/>
@@ -12469,11 +12750,11 @@
         <v>166</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-39</v>
       </c>
       <c r="M96" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>127</v>
       </c>
       <c r="N96" s="1"/>
@@ -12490,26 +12771,26 @@
         <v>0</v>
       </c>
       <c r="W96" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>25.4</v>
       </c>
       <c r="X96" s="5">
-        <f t="shared" ref="X96:X100" si="38">11*W96-V96-U96-T96-S96-R96-Q96-O96-F96-AB96</f>
+        <f t="shared" ref="X96:X100" si="41">11*W96-V96-U96-T96-S96-R96-Q96-O96-F96-AB96</f>
         <v>157.39999999999998</v>
       </c>
       <c r="Y96" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>157.39999999999998</v>
       </c>
       <c r="Z96" s="5"/>
       <c r="AA96" s="5"/>
       <c r="AB96" s="5"/>
       <c r="AC96" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD96" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.8031496062992129</v>
       </c>
       <c r="AE96" s="1">
@@ -12538,18 +12819,21 @@
       </c>
       <c r="AM96" s="1"/>
       <c r="AN96" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>47</v>
       </c>
       <c r="AO96" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP96" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ96" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR96" s="1"/>
       <c r="AS96" s="1"/>
       <c r="AT96" s="1"/>
@@ -12589,11 +12873,11 @@
         <v>64</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2</v>
       </c>
       <c r="M97" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>62</v>
       </c>
       <c r="N97" s="1"/>
@@ -12610,7 +12894,7 @@
         <v>5.039999999999992</v>
       </c>
       <c r="W97" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>12.4</v>
       </c>
       <c r="X97" s="5">
@@ -12618,18 +12902,18 @@
         <v>75.600000000000009</v>
       </c>
       <c r="Y97" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>75.600000000000009</v>
       </c>
       <c r="Z97" s="5"/>
       <c r="AA97" s="5"/>
       <c r="AB97" s="5"/>
       <c r="AC97" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>8</v>
       </c>
       <c r="AD97" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1.9032258064516121</v>
       </c>
       <c r="AE97" s="1">
@@ -12658,18 +12942,21 @@
       </c>
       <c r="AM97" s="1"/>
       <c r="AN97" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>23</v>
       </c>
       <c r="AO97" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP97" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ97" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR97" s="1"/>
       <c r="AS97" s="1"/>
       <c r="AT97" s="1"/>
@@ -12711,11 +12998,11 @@
         <v>212</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-32</v>
       </c>
       <c r="M98" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>174</v>
       </c>
       <c r="N98" s="1"/>
@@ -12734,15 +13021,15 @@
         <v>0</v>
       </c>
       <c r="W98" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>34.799999999999997</v>
       </c>
       <c r="X98" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>206.79999999999995</v>
       </c>
       <c r="Y98" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>106.79999999999995</v>
       </c>
       <c r="Z98" s="5"/>
@@ -12751,11 +13038,11 @@
       </c>
       <c r="AB98" s="5"/>
       <c r="AC98" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD98" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.0574712643678161</v>
       </c>
       <c r="AE98" s="1">
@@ -12784,18 +13071,21 @@
       </c>
       <c r="AM98" s="1"/>
       <c r="AN98" s="1">
-        <f t="shared" si="31"/>
-        <v>7</v>
-      </c>
-      <c r="AO98" s="1">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AP98" s="1">
         <f t="shared" si="33"/>
         <v>7</v>
       </c>
-      <c r="AQ98" s="1"/>
+      <c r="AO98" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AP98" s="1">
+        <f t="shared" si="35"/>
+        <v>7</v>
+      </c>
+      <c r="AQ98" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR98" s="1"/>
       <c r="AS98" s="1"/>
       <c r="AT98" s="1"/>
@@ -12837,11 +13127,11 @@
         <v>192</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-36</v>
       </c>
       <c r="M99" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>156</v>
       </c>
       <c r="N99" s="1"/>
@@ -12858,26 +13148,26 @@
         <v>0</v>
       </c>
       <c r="W99" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>31.2</v>
       </c>
       <c r="X99" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>156.21999999999997</v>
       </c>
       <c r="Y99" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>156.21999999999997</v>
       </c>
       <c r="Z99" s="5"/>
       <c r="AA99" s="5"/>
       <c r="AB99" s="5"/>
       <c r="AC99" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD99" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.9929487179487184</v>
       </c>
       <c r="AE99" s="1">
@@ -12906,18 +13196,21 @@
       </c>
       <c r="AM99" s="1"/>
       <c r="AN99" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>11</v>
       </c>
       <c r="AO99" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP99" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ99" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR99" s="1"/>
       <c r="AS99" s="1"/>
       <c r="AT99" s="1"/>
@@ -12959,11 +13252,11 @@
         <v>171</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-30</v>
       </c>
       <c r="M100" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>137</v>
       </c>
       <c r="N100" s="1"/>
@@ -12982,26 +13275,26 @@
         <v>9.6000000000000227</v>
       </c>
       <c r="W100" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>27.4</v>
       </c>
       <c r="X100" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>152.79999999999995</v>
       </c>
       <c r="Y100" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>152.79999999999995</v>
       </c>
       <c r="Z100" s="5"/>
       <c r="AA100" s="5"/>
       <c r="AB100" s="5"/>
       <c r="AC100" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD100" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.4233576642335777</v>
       </c>
       <c r="AE100" s="1">
@@ -13030,18 +13323,21 @@
       </c>
       <c r="AM100" s="1"/>
       <c r="AN100" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>11</v>
       </c>
       <c r="AO100" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP100" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ100" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ100" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR100" s="1"/>
       <c r="AS100" s="1"/>
       <c r="AT100" s="1"/>
@@ -13083,11 +13379,11 @@
         <v>154</v>
       </c>
       <c r="L101" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-48</v>
       </c>
       <c r="M101" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>101</v>
       </c>
       <c r="N101" s="13"/>
@@ -13106,23 +13402,23 @@
         <v>0</v>
       </c>
       <c r="W101" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>20.2</v>
       </c>
       <c r="X101" s="15"/>
       <c r="Y101" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z101" s="15"/>
       <c r="AA101" s="15"/>
       <c r="AB101" s="15"/>
       <c r="AC101" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>3.8613861386138617</v>
       </c>
       <c r="AD101" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.8613861386138617</v>
       </c>
       <c r="AE101" s="13">
@@ -13151,18 +13447,21 @@
       </c>
       <c r="AM101" s="13"/>
       <c r="AN101" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO101" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP101" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ101" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR101" s="1"/>
       <c r="AS101" s="1"/>
       <c r="AT101" s="1"/>
@@ -13204,11 +13503,11 @@
         <v>20</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L133" si="39">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="42">E102-K102</f>
         <v>-4</v>
       </c>
       <c r="M102" s="1">
-        <f t="shared" ref="M102:M133" si="40">E102-N102+P102</f>
+        <f t="shared" ref="M102:M133" si="43">E102-N102+P102</f>
         <v>8</v>
       </c>
       <c r="N102" s="1"/>
@@ -13227,23 +13526,23 @@
         <v>0</v>
       </c>
       <c r="W102" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.6</v>
       </c>
       <c r="X102" s="5"/>
       <c r="Y102" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z102" s="5"/>
       <c r="AA102" s="5"/>
       <c r="AB102" s="5"/>
       <c r="AC102" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>18.75</v>
       </c>
       <c r="AD102" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>18.75</v>
       </c>
       <c r="AE102" s="1">
@@ -13272,18 +13571,21 @@
       </c>
       <c r="AM102" s="1"/>
       <c r="AN102" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO102" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP102" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ102" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ102" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR102" s="1"/>
       <c r="AS102" s="1"/>
       <c r="AT102" s="1"/>
@@ -13325,11 +13627,11 @@
         <v>21.8</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-9.0980000000000008</v>
       </c>
       <c r="M103" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12.702</v>
       </c>
       <c r="N103" s="1"/>
@@ -13346,26 +13648,26 @@
         <v>0</v>
       </c>
       <c r="W103" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.5404</v>
       </c>
       <c r="X103" s="5">
-        <f t="shared" ref="X103" si="41">11*W103-V103-U103-T103-S103-R103-Q103-O103-F103-AB103</f>
+        <f t="shared" ref="X103" si="44">11*W103-V103-U103-T103-S103-R103-Q103-O103-F103-AB103</f>
         <v>7.6183000000000023</v>
       </c>
       <c r="Y103" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.6183000000000023</v>
       </c>
       <c r="Z103" s="5"/>
       <c r="AA103" s="5"/>
       <c r="AB103" s="5"/>
       <c r="AC103" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD103" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8.0011415525114149</v>
       </c>
       <c r="AE103" s="1">
@@ -13394,18 +13696,21 @@
       </c>
       <c r="AM103" s="1"/>
       <c r="AN103" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>8</v>
       </c>
       <c r="AO103" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP103" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ103" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ103" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR103" s="1"/>
       <c r="AS103" s="1"/>
       <c r="AT103" s="1"/>
@@ -13443,11 +13748,11 @@
         <v>182</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-182</v>
       </c>
       <c r="M104" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N104" s="1"/>
@@ -13464,23 +13769,23 @@
         <v>0</v>
       </c>
       <c r="W104" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X104" s="5"/>
       <c r="Y104" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z104" s="5"/>
       <c r="AA104" s="5"/>
       <c r="AB104" s="5"/>
       <c r="AC104" s="1" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD104" s="1" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE104" s="1">
@@ -13509,18 +13814,21 @@
       </c>
       <c r="AM104" s="1"/>
       <c r="AN104" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO104" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP104" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ104" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ104" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR104" s="1"/>
       <c r="AS104" s="1"/>
       <c r="AT104" s="1"/>
@@ -13550,11 +13858,11 @@
       <c r="J105" s="13"/>
       <c r="K105" s="13"/>
       <c r="L105" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M105" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N105" s="13"/>
@@ -13571,23 +13879,23 @@
         <v>0</v>
       </c>
       <c r="W105" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X105" s="15"/>
       <c r="Y105" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z105" s="15"/>
       <c r="AA105" s="15"/>
       <c r="AB105" s="15"/>
       <c r="AC105" s="13" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD105" s="13" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE105" s="13">
@@ -13618,18 +13926,21 @@
         <v>61</v>
       </c>
       <c r="AN105" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO105" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP105" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ105" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ105" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR105" s="1"/>
       <c r="AS105" s="1"/>
       <c r="AT105" s="1"/>
@@ -13671,11 +13982,11 @@
         <v>413</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-120</v>
       </c>
       <c r="M106" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>293</v>
       </c>
       <c r="N106" s="1"/>
@@ -13692,15 +14003,15 @@
         <v>0</v>
       </c>
       <c r="W106" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>58.6</v>
       </c>
       <c r="X106" s="5">
-        <f t="shared" ref="X106:X117" si="42">11*W106-V106-U106-T106-S106-R106-Q106-O106-F106-AB106</f>
+        <f t="shared" ref="X106:X117" si="45">11*W106-V106-U106-T106-S106-R106-Q106-O106-F106-AB106</f>
         <v>358.6</v>
       </c>
       <c r="Y106" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>158.60000000000002</v>
       </c>
       <c r="Z106" s="5"/>
@@ -13709,11 +14020,11 @@
       </c>
       <c r="AB106" s="5"/>
       <c r="AC106" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD106" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.8805460750853245</v>
       </c>
       <c r="AE106" s="1">
@@ -13742,18 +14053,21 @@
       </c>
       <c r="AM106" s="1"/>
       <c r="AN106" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>13</v>
       </c>
       <c r="AO106" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP106" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>16</v>
       </c>
-      <c r="AQ106" s="1"/>
+      <c r="AQ106" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR106" s="1"/>
       <c r="AS106" s="1"/>
       <c r="AT106" s="1"/>
@@ -13795,11 +14109,11 @@
         <v>343</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-332</v>
       </c>
       <c r="M107" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>11</v>
       </c>
       <c r="N107" s="1"/>
@@ -13816,23 +14130,23 @@
         <v>0</v>
       </c>
       <c r="W107" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="X107" s="5"/>
       <c r="Y107" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z107" s="5"/>
       <c r="AA107" s="5"/>
       <c r="AB107" s="5"/>
       <c r="AC107" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>71.590909090909037</v>
       </c>
       <c r="AD107" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>71.590909090909037</v>
       </c>
       <c r="AE107" s="1">
@@ -13861,18 +14175,21 @@
       </c>
       <c r="AM107" s="1"/>
       <c r="AN107" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO107" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP107" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ107" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ107" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR107" s="1"/>
       <c r="AS107" s="1"/>
       <c r="AT107" s="1"/>
@@ -13914,11 +14231,11 @@
         <v>153</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-83</v>
       </c>
       <c r="M108" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>70</v>
       </c>
       <c r="N108" s="1"/>
@@ -13935,7 +14252,7 @@
         <v>0</v>
       </c>
       <c r="W108" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>14</v>
       </c>
       <c r="X108" s="5">
@@ -13943,18 +14260,18 @@
         <v>80</v>
       </c>
       <c r="Y108" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>80</v>
       </c>
       <c r="Z108" s="5"/>
       <c r="AA108" s="5"/>
       <c r="AB108" s="5"/>
       <c r="AC108" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="AD108" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.2857142857142856</v>
       </c>
       <c r="AE108" s="1">
@@ -13983,18 +14300,21 @@
       </c>
       <c r="AM108" s="1"/>
       <c r="AN108" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>14</v>
       </c>
       <c r="AO108" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP108" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ108" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ108" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR108" s="1"/>
       <c r="AS108" s="1"/>
       <c r="AT108" s="1"/>
@@ -14036,11 +14356,11 @@
         <v>270.60000000000002</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-18.992000000000019</v>
       </c>
       <c r="M109" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>251.608</v>
       </c>
       <c r="N109" s="1"/>
@@ -14057,26 +14377,26 @@
         <v>0</v>
       </c>
       <c r="W109" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>50.321600000000004</v>
       </c>
       <c r="X109" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>241.33159999999998</v>
       </c>
       <c r="Y109" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>241.33159999999998</v>
       </c>
       <c r="Z109" s="5"/>
       <c r="AA109" s="5"/>
       <c r="AB109" s="5"/>
       <c r="AC109" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD109" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>6.2042144923849794</v>
       </c>
       <c r="AE109" s="1">
@@ -14105,18 +14425,21 @@
       </c>
       <c r="AM109" s="1"/>
       <c r="AN109" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>241</v>
       </c>
       <c r="AO109" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP109" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ109" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ109" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR109" s="1"/>
       <c r="AS109" s="1"/>
       <c r="AT109" s="1"/>
@@ -14158,11 +14481,11 @@
         <v>143.78</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-32.738</v>
       </c>
       <c r="M110" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>67.762</v>
       </c>
       <c r="N110" s="1"/>
@@ -14181,26 +14504,26 @@
         <v>0</v>
       </c>
       <c r="W110" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>13.5524</v>
       </c>
       <c r="X110" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>80.849400000000003</v>
       </c>
       <c r="Y110" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>80.849400000000003</v>
       </c>
       <c r="Z110" s="5"/>
       <c r="AA110" s="5"/>
       <c r="AB110" s="5"/>
       <c r="AC110" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD110" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.034311265901243</v>
       </c>
       <c r="AE110" s="1">
@@ -14229,18 +14552,21 @@
       </c>
       <c r="AM110" s="1"/>
       <c r="AN110" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>81</v>
       </c>
       <c r="AO110" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP110" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ110" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ110" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR110" s="1"/>
       <c r="AS110" s="1"/>
       <c r="AT110" s="1"/>
@@ -14282,11 +14608,11 @@
         <v>260.5</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-66.996000000000009</v>
       </c>
       <c r="M111" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>193.50399999999999</v>
       </c>
       <c r="N111" s="1"/>
@@ -14303,15 +14629,15 @@
         <v>0</v>
       </c>
       <c r="W111" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>38.700800000000001</v>
       </c>
       <c r="X111" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>230.21379999999999</v>
       </c>
       <c r="Y111" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>130.21379999999999</v>
       </c>
       <c r="Z111" s="5"/>
@@ -14320,11 +14646,11 @@
       </c>
       <c r="AB111" s="5"/>
       <c r="AC111" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD111" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.0514459649412933</v>
       </c>
       <c r="AE111" s="1">
@@ -14353,18 +14679,21 @@
       </c>
       <c r="AM111" s="1"/>
       <c r="AN111" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>130</v>
       </c>
       <c r="AO111" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP111" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>100</v>
       </c>
-      <c r="AQ111" s="1"/>
+      <c r="AQ111" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR111" s="1"/>
       <c r="AS111" s="1"/>
       <c r="AT111" s="1"/>
@@ -14406,11 +14735,11 @@
         <v>99</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-23</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>76</v>
       </c>
       <c r="N112" s="1"/>
@@ -14427,7 +14756,7 @@
         <v>0</v>
       </c>
       <c r="W112" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>15.2</v>
       </c>
       <c r="X112" s="5">
@@ -14435,18 +14764,18 @@
         <v>90</v>
       </c>
       <c r="Y112" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>90</v>
       </c>
       <c r="Z112" s="5"/>
       <c r="AA112" s="5"/>
       <c r="AB112" s="5"/>
       <c r="AC112" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD112" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.0789473684210531</v>
       </c>
       <c r="AE112" s="1">
@@ -14475,18 +14804,21 @@
       </c>
       <c r="AM112" s="1"/>
       <c r="AN112" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>27</v>
       </c>
       <c r="AO112" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP112" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ112" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ112" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR112" s="1"/>
       <c r="AS112" s="1"/>
       <c r="AT112" s="1"/>
@@ -14528,11 +14860,11 @@
         <v>1.3</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>7.9999999999999849E-2</v>
       </c>
       <c r="M113" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>1.38</v>
       </c>
       <c r="N113" s="1"/>
@@ -14549,23 +14881,23 @@
         <v>0</v>
       </c>
       <c r="W113" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.27599999999999997</v>
       </c>
       <c r="X113" s="5"/>
       <c r="Y113" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z113" s="5"/>
       <c r="AA113" s="5"/>
       <c r="AB113" s="5"/>
       <c r="AC113" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>73.865942028985515</v>
       </c>
       <c r="AD113" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>73.865942028985515</v>
       </c>
       <c r="AE113" s="1">
@@ -14594,18 +14926,21 @@
       </c>
       <c r="AM113" s="1"/>
       <c r="AN113" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO113" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP113" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ113" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ113" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR113" s="1"/>
       <c r="AS113" s="1"/>
       <c r="AT113" s="1"/>
@@ -14647,11 +14982,11 @@
         <v>534</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-89</v>
       </c>
       <c r="M114" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>445</v>
       </c>
       <c r="N114" s="1"/>
@@ -14668,26 +15003,26 @@
         <v>47.803999999999959</v>
       </c>
       <c r="W114" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>89</v>
       </c>
       <c r="X114" s="5">
-        <f t="shared" ref="X114:X116" si="43">10*W114-V114-U114-T114-S114-R114-Q114-O114-F114-AB114</f>
+        <f t="shared" ref="X114:X116" si="46">10*W114-V114-U114-T114-S114-R114-Q114-O114-F114-AB114</f>
         <v>496.19600000000003</v>
       </c>
       <c r="Y114" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>496.19600000000003</v>
       </c>
       <c r="Z114" s="5"/>
       <c r="AA114" s="5"/>
       <c r="AB114" s="5"/>
       <c r="AC114" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD114" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.4247640449438199</v>
       </c>
       <c r="AE114" s="1">
@@ -14716,18 +15051,21 @@
       </c>
       <c r="AM114" s="1"/>
       <c r="AN114" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>139</v>
       </c>
       <c r="AO114" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP114" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ114" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ114" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR114" s="1"/>
       <c r="AS114" s="1"/>
       <c r="AT114" s="1"/>
@@ -14769,11 +15107,11 @@
         <v>565</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-108</v>
       </c>
       <c r="M115" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>457</v>
       </c>
       <c r="N115" s="1"/>
@@ -14790,15 +15128,15 @@
         <v>17.9316</v>
       </c>
       <c r="W115" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>91.4</v>
       </c>
       <c r="X115" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>593.3424</v>
       </c>
       <c r="Y115" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>293.3424</v>
       </c>
       <c r="Z115" s="5"/>
@@ -14807,11 +15145,11 @@
       </c>
       <c r="AB115" s="5"/>
       <c r="AC115" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD115" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.508288840262582</v>
       </c>
       <c r="AE115" s="1">
@@ -14840,18 +15178,21 @@
       </c>
       <c r="AM115" s="1"/>
       <c r="AN115" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>82</v>
       </c>
       <c r="AO115" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP115" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>84</v>
       </c>
-      <c r="AQ115" s="1"/>
+      <c r="AQ115" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR115" s="1"/>
       <c r="AS115" s="1"/>
       <c r="AT115" s="1"/>
@@ -14893,11 +15234,11 @@
         <v>871</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-126</v>
       </c>
       <c r="M116" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>685</v>
       </c>
       <c r="N116" s="1"/>
@@ -14916,15 +15257,15 @@
         <v>167.92099999999979</v>
       </c>
       <c r="W116" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>137</v>
       </c>
       <c r="X116" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>793.57900000000018</v>
       </c>
       <c r="Y116" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>393.57900000000018</v>
       </c>
       <c r="Z116" s="5"/>
@@ -14933,11 +15274,11 @@
       </c>
       <c r="AB116" s="5"/>
       <c r="AC116" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD116" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.2074525547445241</v>
       </c>
       <c r="AE116" s="1">
@@ -14966,18 +15307,21 @@
       </c>
       <c r="AM116" s="1"/>
       <c r="AN116" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>110</v>
       </c>
       <c r="AO116" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP116" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>112</v>
       </c>
-      <c r="AQ116" s="1"/>
+      <c r="AQ116" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR116" s="1"/>
       <c r="AS116" s="1"/>
       <c r="AT116" s="1"/>
@@ -15019,11 +15363,11 @@
         <v>125</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-59</v>
       </c>
       <c r="M117" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>66</v>
       </c>
       <c r="N117" s="1"/>
@@ -15040,26 +15384,26 @@
         <v>0</v>
       </c>
       <c r="W117" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>13.2</v>
       </c>
       <c r="X117" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>71.179999999999978</v>
       </c>
       <c r="Y117" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>71.179999999999978</v>
       </c>
       <c r="Z117" s="5"/>
       <c r="AA117" s="5"/>
       <c r="AB117" s="5"/>
       <c r="AC117" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD117" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.6075757575757583</v>
       </c>
       <c r="AE117" s="1">
@@ -15088,18 +15432,21 @@
       </c>
       <c r="AM117" s="1"/>
       <c r="AN117" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>6</v>
       </c>
       <c r="AO117" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP117" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ117" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ117" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR117" s="1"/>
       <c r="AS117" s="1"/>
       <c r="AT117" s="1"/>
@@ -15141,11 +15488,11 @@
         <v>15.8</v>
       </c>
       <c r="L118" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-7.67</v>
       </c>
       <c r="M118" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>8.1300000000000008</v>
       </c>
       <c r="N118" s="13"/>
@@ -15162,23 +15509,23 @@
         <v>0</v>
       </c>
       <c r="W118" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.6260000000000001</v>
       </c>
       <c r="X118" s="15"/>
       <c r="Y118" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z118" s="15"/>
       <c r="AA118" s="15"/>
       <c r="AB118" s="15"/>
       <c r="AC118" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>37.321033210332097</v>
       </c>
       <c r="AD118" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>37.321033210332097</v>
       </c>
       <c r="AE118" s="13">
@@ -15209,18 +15556,21 @@
         <v>52</v>
       </c>
       <c r="AN118" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO118" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP118" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ118" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ118" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR118" s="1"/>
       <c r="AS118" s="1"/>
       <c r="AT118" s="1"/>
@@ -15262,11 +15612,11 @@
         <v>120</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-47.480000000000004</v>
       </c>
       <c r="M119" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>72.52</v>
       </c>
       <c r="N119" s="1"/>
@@ -15283,26 +15633,26 @@
         <v>0</v>
       </c>
       <c r="W119" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>14.504</v>
       </c>
       <c r="X119" s="5">
-        <f t="shared" ref="X119:X131" si="44">11*W119-V119-U119-T119-S119-R119-Q119-O119-F119-AB119</f>
+        <f t="shared" ref="X119:X131" si="47">11*W119-V119-U119-T119-S119-R119-Q119-O119-F119-AB119</f>
         <v>89.631999999999977</v>
       </c>
       <c r="Y119" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>89.631999999999977</v>
       </c>
       <c r="Z119" s="5"/>
       <c r="AA119" s="5"/>
       <c r="AB119" s="5"/>
       <c r="AC119" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD119" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.8201875344732494</v>
       </c>
       <c r="AE119" s="1">
@@ -15331,18 +15681,21 @@
       </c>
       <c r="AM119" s="1"/>
       <c r="AN119" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>90</v>
       </c>
       <c r="AO119" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP119" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ119" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ119" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR119" s="1"/>
       <c r="AS119" s="1"/>
       <c r="AT119" s="1"/>
@@ -15384,11 +15737,11 @@
         <v>205.95500000000001</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-18.413000000000011</v>
       </c>
       <c r="M120" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>51.586999999999989</v>
       </c>
       <c r="N120" s="1"/>
@@ -15407,7 +15760,7 @@
         <v>29.809799999999981</v>
       </c>
       <c r="W120" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>10.317399999999997</v>
       </c>
       <c r="X120" s="5">
@@ -15415,18 +15768,18 @@
         <v>63.256000000000007</v>
       </c>
       <c r="Y120" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>63.256000000000007</v>
       </c>
       <c r="Z120" s="5"/>
       <c r="AA120" s="5"/>
       <c r="AB120" s="5"/>
       <c r="AC120" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7.0000000000000009</v>
       </c>
       <c r="AD120" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.86899800337294109</v>
       </c>
       <c r="AE120" s="1">
@@ -15455,18 +15808,21 @@
       </c>
       <c r="AM120" s="1"/>
       <c r="AN120" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>63</v>
       </c>
       <c r="AO120" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP120" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ120" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ120" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR120" s="1"/>
       <c r="AS120" s="1"/>
       <c r="AT120" s="1"/>
@@ -15508,11 +15864,11 @@
         <v>102</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-33</v>
       </c>
       <c r="M121" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>69</v>
       </c>
       <c r="N121" s="1"/>
@@ -15529,26 +15885,26 @@
         <v>48.040000000000013</v>
       </c>
       <c r="W121" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>13.8</v>
       </c>
       <c r="X121" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>78.199999999999989</v>
       </c>
       <c r="Y121" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>78.199999999999989</v>
       </c>
       <c r="Z121" s="5"/>
       <c r="AA121" s="5"/>
       <c r="AB121" s="5"/>
       <c r="AC121" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD121" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.3333333333333348</v>
       </c>
       <c r="AE121" s="1">
@@ -15577,18 +15933,21 @@
       </c>
       <c r="AM121" s="1"/>
       <c r="AN121" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>7</v>
       </c>
       <c r="AO121" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP121" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ121" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ121" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR121" s="1"/>
       <c r="AS121" s="1"/>
       <c r="AT121" s="1"/>
@@ -15630,11 +15989,11 @@
         <v>149</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-62</v>
       </c>
       <c r="M122" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>87</v>
       </c>
       <c r="N122" s="1"/>
@@ -15651,7 +16010,7 @@
         <v>45.600000000000009</v>
       </c>
       <c r="W122" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>17.399999999999999</v>
       </c>
       <c r="X122" s="5">
@@ -15659,18 +16018,18 @@
         <v>103.39999999999998</v>
       </c>
       <c r="Y122" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>103.39999999999998</v>
       </c>
       <c r="Z122" s="5"/>
       <c r="AA122" s="5"/>
       <c r="AB122" s="5"/>
       <c r="AC122" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD122" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.057471264367817</v>
       </c>
       <c r="AE122" s="1">
@@ -15701,18 +16060,21 @@
         <v>168</v>
       </c>
       <c r="AN122" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>9</v>
       </c>
       <c r="AO122" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP122" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ122" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ122" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR122" s="1"/>
       <c r="AS122" s="1"/>
       <c r="AT122" s="1"/>
@@ -15754,11 +16116,11 @@
         <v>495.476</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-4.9429999999999836</v>
       </c>
       <c r="M123" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>77.456999999999994</v>
       </c>
       <c r="N123" s="1"/>
@@ -15777,26 +16139,26 @@
         <v>67.74599999999991</v>
       </c>
       <c r="W123" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>15.491399999999999</v>
       </c>
       <c r="X123" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>83.946400000000068</v>
       </c>
       <c r="Y123" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>83.946400000000068</v>
       </c>
       <c r="Z123" s="5"/>
       <c r="AA123" s="5"/>
       <c r="AB123" s="5"/>
       <c r="AC123" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD123" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.5810966084408076</v>
       </c>
       <c r="AE123" s="1">
@@ -15827,18 +16189,21 @@
         <v>170</v>
       </c>
       <c r="AN123" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>84</v>
       </c>
       <c r="AO123" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP123" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ123" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ123" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR123" s="1"/>
       <c r="AS123" s="1"/>
       <c r="AT123" s="1"/>
@@ -15880,11 +16245,11 @@
         <v>664.44100000000003</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-45.835000000000036</v>
       </c>
       <c r="M124" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>618.60599999999999</v>
       </c>
       <c r="N124" s="1"/>
@@ -15901,15 +16266,15 @@
         <v>84.844600000000128</v>
       </c>
       <c r="W124" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>123.7212</v>
       </c>
       <c r="X124" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>724.38959999999986</v>
       </c>
       <c r="Y124" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>324.38959999999986</v>
       </c>
       <c r="Z124" s="5"/>
@@ -15918,11 +16283,11 @@
       </c>
       <c r="AB124" s="5"/>
       <c r="AC124" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD124" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.1449840447716326</v>
       </c>
       <c r="AE124" s="1">
@@ -15951,18 +16316,21 @@
       </c>
       <c r="AM124" s="1"/>
       <c r="AN124" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>324</v>
       </c>
       <c r="AO124" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP124" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>400</v>
       </c>
-      <c r="AQ124" s="1"/>
+      <c r="AQ124" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR124" s="1"/>
       <c r="AS124" s="1"/>
       <c r="AT124" s="1"/>
@@ -16004,11 +16372,11 @@
         <v>75.8</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-5.3520000000000039</v>
       </c>
       <c r="M125" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>70.447999999999993</v>
       </c>
       <c r="N125" s="1"/>
@@ -16025,23 +16393,23 @@
         <v>0</v>
       </c>
       <c r="W125" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>14.089599999999999</v>
       </c>
       <c r="X125" s="5"/>
       <c r="Y125" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z125" s="5"/>
       <c r="AA125" s="5"/>
       <c r="AB125" s="5"/>
       <c r="AC125" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>24.388343175107885</v>
       </c>
       <c r="AD125" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>24.388343175107885</v>
       </c>
       <c r="AE125" s="1">
@@ -16072,18 +16440,21 @@
         <v>188</v>
       </c>
       <c r="AN125" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO125" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP125" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ125" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ125" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR125" s="1"/>
       <c r="AS125" s="1"/>
       <c r="AT125" s="1"/>
@@ -16125,11 +16496,11 @@
         <v>1111.5999999999999</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-97.231999999999857</v>
       </c>
       <c r="M126" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>1014.3680000000001</v>
       </c>
       <c r="N126" s="1"/>
@@ -16146,23 +16517,23 @@
         <v>0</v>
       </c>
       <c r="W126" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>202.87360000000001</v>
       </c>
       <c r="X126" s="5"/>
       <c r="Y126" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z126" s="5"/>
       <c r="AA126" s="5"/>
       <c r="AB126" s="5"/>
       <c r="AC126" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>13.924734415912171</v>
       </c>
       <c r="AD126" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>13.924734415912171</v>
       </c>
       <c r="AE126" s="1">
@@ -16191,18 +16562,21 @@
       </c>
       <c r="AM126" s="1"/>
       <c r="AN126" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO126" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP126" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ126" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ126" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR126" s="1"/>
       <c r="AS126" s="1"/>
       <c r="AT126" s="1"/>
@@ -16244,11 +16618,11 @@
         <v>218</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-21</v>
       </c>
       <c r="M127" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>197</v>
       </c>
       <c r="N127" s="1"/>
@@ -16267,7 +16641,7 @@
         <v>80.606000000000051</v>
       </c>
       <c r="W127" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>39.4</v>
       </c>
       <c r="X127" s="5">
@@ -16275,18 +16649,18 @@
         <v>222.99399999999991</v>
       </c>
       <c r="Y127" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>222.99399999999991</v>
       </c>
       <c r="Z127" s="5"/>
       <c r="AA127" s="5"/>
       <c r="AB127" s="5"/>
       <c r="AC127" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="AD127" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.3402538071066004</v>
       </c>
       <c r="AE127" s="1">
@@ -16315,18 +16689,21 @@
       </c>
       <c r="AM127" s="1"/>
       <c r="AN127" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>67</v>
       </c>
       <c r="AO127" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP127" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ127" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ127" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR127" s="1"/>
       <c r="AS127" s="1"/>
       <c r="AT127" s="1"/>
@@ -16368,11 +16745,11 @@
         <v>143</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-25</v>
       </c>
       <c r="M128" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>118</v>
       </c>
       <c r="N128" s="1"/>
@@ -16389,26 +16766,26 @@
         <v>35.799999999999983</v>
       </c>
       <c r="W128" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>23.6</v>
       </c>
       <c r="X128" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>47.399999999999977</v>
       </c>
       <c r="Y128" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>47.399999999999977</v>
       </c>
       <c r="Z128" s="5"/>
       <c r="AA128" s="5"/>
       <c r="AB128" s="5"/>
       <c r="AC128" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD128" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8.9915254237288149</v>
       </c>
       <c r="AE128" s="1">
@@ -16437,18 +16814,21 @@
       </c>
       <c r="AM128" s="1"/>
       <c r="AN128" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>14</v>
       </c>
       <c r="AO128" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP128" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ128" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ128" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR128" s="1"/>
       <c r="AS128" s="1"/>
       <c r="AT128" s="1"/>
@@ -16490,11 +16870,11 @@
         <v>92.2</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-10.945000000000007</v>
       </c>
       <c r="M129" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>81.254999999999995</v>
       </c>
       <c r="N129" s="1"/>
@@ -16511,7 +16891,7 @@
         <v>17.2804</v>
       </c>
       <c r="W129" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>16.250999999999998</v>
       </c>
       <c r="X129" s="5">
@@ -16519,18 +16899,18 @@
         <v>92.068600000000004</v>
       </c>
       <c r="Y129" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>92.068600000000004</v>
       </c>
       <c r="Z129" s="5"/>
       <c r="AA129" s="5"/>
       <c r="AB129" s="5"/>
       <c r="AC129" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>10</v>
       </c>
       <c r="AD129" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.3345886406990344</v>
       </c>
       <c r="AE129" s="1">
@@ -16559,18 +16939,21 @@
       </c>
       <c r="AM129" s="1"/>
       <c r="AN129" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>92</v>
       </c>
       <c r="AO129" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP129" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ129" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ129" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR129" s="1"/>
       <c r="AS129" s="1"/>
       <c r="AT129" s="1"/>
@@ -16612,11 +16995,11 @@
         <v>69</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-10</v>
       </c>
       <c r="M130" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>59</v>
       </c>
       <c r="N130" s="1"/>
@@ -16633,26 +17016,26 @@
         <v>20</v>
       </c>
       <c r="W130" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>11.8</v>
       </c>
       <c r="X130" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>48.800000000000011</v>
       </c>
       <c r="Y130" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>48.800000000000011</v>
       </c>
       <c r="Z130" s="5"/>
       <c r="AA130" s="5"/>
       <c r="AB130" s="5"/>
       <c r="AC130" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD130" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>6.8644067796610164</v>
       </c>
       <c r="AE130" s="1">
@@ -16681,18 +17064,21 @@
       </c>
       <c r="AM130" s="1"/>
       <c r="AN130" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>15</v>
       </c>
       <c r="AO130" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP130" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ130" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ130" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR130" s="1"/>
       <c r="AS130" s="1"/>
       <c r="AT130" s="1"/>
@@ -16734,11 +17120,11 @@
         <v>66</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-9</v>
       </c>
       <c r="M131" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>57</v>
       </c>
       <c r="N131" s="1"/>
@@ -16755,26 +17141,26 @@
         <v>46.800000000000011</v>
       </c>
       <c r="W131" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>11.4</v>
       </c>
       <c r="X131" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>17.599999999999994</v>
       </c>
       <c r="Y131" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>17.599999999999994</v>
       </c>
       <c r="Z131" s="5"/>
       <c r="AA131" s="5"/>
       <c r="AB131" s="5"/>
       <c r="AC131" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AD131" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>9.4561403508771935</v>
       </c>
       <c r="AE131" s="1">
@@ -16803,18 +17189,21 @@
       </c>
       <c r="AM131" s="1"/>
       <c r="AN131" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2</v>
       </c>
       <c r="AO131" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP131" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ131" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ131" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR131" s="1"/>
       <c r="AS131" s="1"/>
       <c r="AT131" s="1"/>
@@ -16844,11 +17233,11 @@
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
       <c r="L132" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M132" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N132" s="1"/>
@@ -16865,23 +17254,23 @@
         <v>0</v>
       </c>
       <c r="W132" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X132" s="5"/>
       <c r="Y132" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z132" s="5"/>
       <c r="AA132" s="5"/>
       <c r="AB132" s="5"/>
       <c r="AC132" s="1" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD132" s="1" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE132" s="1">
@@ -16912,18 +17301,21 @@
         <v>180</v>
       </c>
       <c r="AN132" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO132" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP132" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ132" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ132" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR132" s="1"/>
       <c r="AS132" s="1"/>
       <c r="AT132" s="1"/>
@@ -16953,11 +17345,11 @@
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
       <c r="L133" s="1">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M133" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N133" s="1"/>
@@ -16974,23 +17366,23 @@
         <v>0</v>
       </c>
       <c r="W133" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X133" s="5"/>
       <c r="Y133" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z133" s="5"/>
       <c r="AA133" s="5"/>
       <c r="AB133" s="5"/>
       <c r="AC133" s="1" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD133" s="1" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE133" s="1">
@@ -17021,18 +17413,21 @@
         <v>180</v>
       </c>
       <c r="AN133" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO133" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP133" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ133" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ133" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR133" s="1"/>
       <c r="AS133" s="1"/>
       <c r="AT133" s="1"/>
@@ -17062,11 +17457,11 @@
       <c r="J134" s="1"/>
       <c r="K134" s="1"/>
       <c r="L134" s="1">
-        <f t="shared" ref="L134" si="45">E134-K134</f>
+        <f t="shared" ref="L134" si="48">E134-K134</f>
         <v>0</v>
       </c>
       <c r="M134" s="1">
-        <f t="shared" ref="M134" si="46">E134-N134+P134</f>
+        <f t="shared" ref="M134" si="49">E134-N134+P134</f>
         <v>0</v>
       </c>
       <c r="N134" s="1"/>
@@ -17083,23 +17478,23 @@
         <v>0</v>
       </c>
       <c r="W134" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X134" s="5"/>
       <c r="Y134" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z134" s="5"/>
       <c r="AA134" s="5"/>
       <c r="AB134" s="5"/>
       <c r="AC134" s="1" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD134" s="1" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE134" s="1">
@@ -17130,18 +17525,21 @@
         <v>180</v>
       </c>
       <c r="AN134" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AO134" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AP134" s="1">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AQ134" s="1"/>
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AQ134" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="AR134" s="1"/>
       <c r="AS134" s="1"/>
       <c r="AT134" s="1"/>
